--- a/data/daily_age_gender/【2025年9月】デイリー年齢性別.xlsx
+++ b/data/daily_age_gender/【2025年9月】デイリー年齢性別.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="49">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -23,7 +23,7 @@
     <t>レポート終了日</t>
   </si>
   <si>
-    <t>広告セット名</t>
+    <t>キャンペーン名</t>
   </si>
   <si>
     <t>年齢</t>
@@ -32,7 +32,7 @@
     <t>性別</t>
   </si>
   <si>
-    <t>広告セットの配信</t>
+    <t>キャンペーンの配信</t>
   </si>
   <si>
     <t>アトリビューション設定</t>
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t>終了日時</t>
-  </si>
-  <si>
-    <t>開始</t>
   </si>
   <si>
     <t>インプレッション</t>
@@ -104,7 +101,8 @@
     <t>2025-09-18</t>
   </si>
   <si>
-    <t>Instagram Post</t>
+    <t>Instagram投稿: 【竹内歯科クリニック】
+＼“治す”だけでなく、“美しく、健やかに”整える／...</t>
   </si>
   <si>
     <t>65+</t>
@@ -119,10 +117,7 @@
     <t>クリックから7日間、または表示から1日間</t>
   </si>
   <si>
-    <t>キャンペーン予算を使用</t>
-  </si>
-  <si>
-    <t>2025-09-11</t>
+    <t>1日</t>
   </si>
   <si>
     <t>female</t>
@@ -149,7 +144,7 @@
     <t>2025-09-17</t>
   </si>
   <si>
-    <t>profile_visit_view</t>
+    <t>actions:link_click</t>
   </si>
   <si>
     <t>2025-09-16</t>
@@ -165,6 +160,9 @@
   </si>
   <si>
     <t>2025-09-12</t>
+  </si>
+  <si>
+    <t>2025-09-11</t>
   </si>
 </sst>
 </file>
@@ -519,10 +517,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AB102"/>
+  <dimension ref="A1:AA102"/>
   <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="20" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -604,31 +602,28 @@
       <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28">
+    </row>
+    <row r="2" spans="1:27">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
         <v>29</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>30</v>
       </c>
-      <c r="E2" t="s">
-        <v>31</v>
-      </c>
       <c r="F2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -636,58 +631,55 @@
       <c r="K2">
         <v>1.25</v>
       </c>
-      <c r="M2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
+      <c r="M2">
+        <v>149</v>
+      </c>
+      <c r="N2" t="s">
+        <v>33</v>
       </c>
       <c r="O2">
         <v>3</v>
       </c>
       <c r="P2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q2">
+        <v>5</v>
       </c>
       <c r="R2">
-        <v>5</v>
-      </c>
-      <c r="S2">
         <v>600</v>
       </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
       <c r="X2">
         <v>0</v>
       </c>
       <c r="Y2">
         <v>0</v>
       </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28">
+    </row>
+    <row r="3" spans="1:27">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
         <v>29</v>
       </c>
-      <c r="D3" t="s">
-        <v>30</v>
-      </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J3">
         <v>3</v>
@@ -695,58 +687,55 @@
       <c r="K3">
         <v>1</v>
       </c>
-      <c r="M3" t="s">
-        <v>34</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
+      <c r="M3">
+        <v>149</v>
+      </c>
+      <c r="N3" t="s">
+        <v>33</v>
       </c>
       <c r="O3">
         <v>6</v>
       </c>
       <c r="P3" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q3">
+        <v>3</v>
+      </c>
+      <c r="R3">
+        <v>2000</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
         <v>35</v>
       </c>
-      <c r="R3">
-        <v>3</v>
-      </c>
-      <c r="S3">
-        <v>2000</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>37</v>
-      </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -754,58 +743,55 @@
       <c r="K4">
         <v>1</v>
       </c>
-      <c r="M4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
+      <c r="M4">
+        <v>149</v>
+      </c>
+      <c r="N4" t="s">
+        <v>33</v>
       </c>
       <c r="O4">
         <v>4</v>
       </c>
       <c r="P4" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q4" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q4">
+        <v>6</v>
+      </c>
+      <c r="R4">
+        <v>666.666667</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
         <v>35</v>
       </c>
-      <c r="R4">
-        <v>6</v>
-      </c>
-      <c r="S4">
-        <v>666.666667</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>37</v>
-      </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J5">
         <v>8</v>
@@ -813,58 +799,55 @@
       <c r="K5">
         <v>1</v>
       </c>
-      <c r="M5" t="s">
-        <v>34</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
+      <c r="M5">
+        <v>149</v>
+      </c>
+      <c r="N5" t="s">
+        <v>33</v>
       </c>
       <c r="O5">
         <v>8</v>
       </c>
       <c r="P5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q5">
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>8</v>
-      </c>
-      <c r="S5">
         <v>1000</v>
       </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
       <c r="X5">
         <v>0</v>
       </c>
       <c r="Y5">
         <v>0</v>
       </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28">
+    </row>
+    <row r="6" spans="1:27">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -872,25 +855,25 @@
       <c r="K6">
         <v>1</v>
       </c>
-      <c r="M6" t="s">
-        <v>34</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
+      <c r="M6">
+        <v>149</v>
+      </c>
+      <c r="N6" t="s">
+        <v>33</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
       </c>
       <c r="R6">
-        <v>1</v>
-      </c>
-      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="W6">
         <v>0</v>
       </c>
       <c r="X6">
@@ -899,31 +882,28 @@
       <c r="Y6">
         <v>0</v>
       </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28">
+    </row>
+    <row r="7" spans="1:27">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J7">
         <v>10</v>
@@ -931,58 +911,55 @@
       <c r="K7">
         <v>1</v>
       </c>
-      <c r="M7" t="s">
-        <v>34</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
+      <c r="M7">
+        <v>149</v>
+      </c>
+      <c r="N7" t="s">
+        <v>33</v>
       </c>
       <c r="O7">
         <v>7</v>
       </c>
       <c r="P7" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q7">
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>10</v>
-      </c>
-      <c r="S7">
         <v>700</v>
       </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
       <c r="X7">
         <v>0</v>
       </c>
       <c r="Y7">
         <v>0</v>
       </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28">
+    </row>
+    <row r="8" spans="1:27">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J8">
         <v>11</v>
@@ -990,58 +967,55 @@
       <c r="K8">
         <v>1</v>
       </c>
-      <c r="M8" t="s">
-        <v>34</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
+      <c r="M8">
+        <v>149</v>
+      </c>
+      <c r="N8" t="s">
+        <v>33</v>
       </c>
       <c r="O8">
         <v>18</v>
       </c>
       <c r="P8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q8">
+        <v>11</v>
       </c>
       <c r="R8">
-        <v>11</v>
-      </c>
-      <c r="S8">
         <v>1636.363636</v>
       </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
       <c r="X8">
         <v>0</v>
       </c>
       <c r="Y8">
         <v>0</v>
       </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28">
+    </row>
+    <row r="9" spans="1:27">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J9">
         <v>5</v>
@@ -1049,58 +1023,55 @@
       <c r="K9">
         <v>1</v>
       </c>
-      <c r="M9" t="s">
-        <v>34</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
+      <c r="M9">
+        <v>149</v>
+      </c>
+      <c r="N9" t="s">
+        <v>33</v>
       </c>
       <c r="O9">
         <v>9</v>
       </c>
       <c r="P9" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q9">
+        <v>5</v>
       </c>
       <c r="R9">
-        <v>5</v>
-      </c>
-      <c r="S9">
         <v>1800</v>
       </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
       <c r="X9">
         <v>0</v>
       </c>
       <c r="Y9">
         <v>0</v>
       </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28">
+    </row>
+    <row r="10" spans="1:27">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J10">
         <v>3</v>
@@ -1108,58 +1079,55 @@
       <c r="K10">
         <v>1</v>
       </c>
-      <c r="M10" t="s">
-        <v>34</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
+      <c r="M10">
+        <v>149</v>
+      </c>
+      <c r="N10" t="s">
+        <v>33</v>
       </c>
       <c r="O10">
         <v>2</v>
       </c>
       <c r="P10" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q10">
+        <v>3</v>
       </c>
       <c r="R10">
-        <v>3</v>
-      </c>
-      <c r="S10">
         <v>666.666667</v>
       </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
       <c r="X10">
         <v>0</v>
       </c>
       <c r="Y10">
         <v>0</v>
       </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28">
+    </row>
+    <row r="11" spans="1:27">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J11">
         <v>7</v>
@@ -1167,58 +1135,55 @@
       <c r="K11">
         <v>1</v>
       </c>
-      <c r="M11" t="s">
-        <v>34</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
+      <c r="M11">
+        <v>149</v>
+      </c>
+      <c r="N11" t="s">
+        <v>33</v>
       </c>
       <c r="O11">
         <v>5</v>
       </c>
       <c r="P11" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q11">
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>7</v>
-      </c>
-      <c r="S11">
         <v>714.285714</v>
       </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
       <c r="X11">
         <v>0</v>
       </c>
       <c r="Y11">
         <v>0</v>
       </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28">
+    </row>
+    <row r="12" spans="1:27">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J12">
         <v>2</v>
@@ -1226,58 +1191,55 @@
       <c r="K12">
         <v>1</v>
       </c>
-      <c r="M12" t="s">
-        <v>34</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
+      <c r="M12">
+        <v>149</v>
+      </c>
+      <c r="N12" t="s">
+        <v>33</v>
       </c>
       <c r="O12">
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q12">
+        <v>2</v>
       </c>
       <c r="R12">
-        <v>2</v>
-      </c>
-      <c r="S12">
         <v>500</v>
       </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
       <c r="X12">
         <v>0</v>
       </c>
       <c r="Y12">
         <v>0</v>
       </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28">
+    </row>
+    <row r="13" spans="1:27">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1285,58 +1247,55 @@
       <c r="K13">
         <v>1</v>
       </c>
-      <c r="M13" t="s">
-        <v>34</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
+      <c r="M13">
+        <v>149</v>
+      </c>
+      <c r="N13" t="s">
+        <v>33</v>
       </c>
       <c r="O13">
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
       </c>
       <c r="R13">
-        <v>1</v>
-      </c>
-      <c r="S13">
         <v>1000</v>
       </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
       <c r="X13">
         <v>0</v>
       </c>
       <c r="Y13">
         <v>0</v>
       </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28">
+    </row>
+    <row r="14" spans="1:27">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J14">
         <v>6</v>
@@ -1344,58 +1303,55 @@
       <c r="K14">
         <v>1</v>
       </c>
-      <c r="M14" t="s">
-        <v>34</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
+      <c r="M14">
+        <v>149</v>
+      </c>
+      <c r="N14" t="s">
+        <v>33</v>
       </c>
       <c r="O14">
         <v>4</v>
       </c>
       <c r="P14" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q14">
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>6</v>
-      </c>
-      <c r="S14">
         <v>666.666667</v>
       </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
       <c r="X14">
         <v>0</v>
       </c>
       <c r="Y14">
         <v>0</v>
       </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28">
+    </row>
+    <row r="15" spans="1:27">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J15">
         <v>7</v>
@@ -1403,58 +1359,55 @@
       <c r="K15">
         <v>1</v>
       </c>
-      <c r="M15" t="s">
-        <v>34</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
+      <c r="M15">
+        <v>149</v>
+      </c>
+      <c r="N15" t="s">
+        <v>33</v>
       </c>
       <c r="O15">
         <v>2</v>
       </c>
       <c r="P15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q15">
+        <v>7</v>
       </c>
       <c r="R15">
-        <v>7</v>
-      </c>
-      <c r="S15">
         <v>285.714286</v>
       </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
       <c r="X15">
         <v>0</v>
       </c>
       <c r="Y15">
         <v>0</v>
       </c>
-      <c r="Z15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28">
+    </row>
+    <row r="16" spans="1:27">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" t="s">
         <v>29</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>30</v>
       </c>
-      <c r="E16" t="s">
-        <v>31</v>
-      </c>
       <c r="F16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J16">
         <v>12</v>
@@ -1462,58 +1415,55 @@
       <c r="K16">
         <v>1.083333</v>
       </c>
-      <c r="M16" t="s">
-        <v>34</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
+      <c r="M16">
+        <v>149</v>
+      </c>
+      <c r="N16" t="s">
+        <v>33</v>
       </c>
       <c r="O16">
         <v>36</v>
       </c>
       <c r="P16" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q16">
+        <v>13</v>
       </c>
       <c r="R16">
-        <v>13</v>
-      </c>
-      <c r="S16">
         <v>2769.230769</v>
       </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
       <c r="X16">
         <v>0</v>
       </c>
       <c r="Y16">
         <v>0</v>
       </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:28">
+    </row>
+    <row r="17" spans="1:27">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" t="s">
         <v>29</v>
       </c>
-      <c r="D17" t="s">
-        <v>30</v>
-      </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J17">
         <v>8</v>
@@ -1521,58 +1471,55 @@
       <c r="K17">
         <v>1</v>
       </c>
-      <c r="M17" t="s">
-        <v>34</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
+      <c r="M17">
+        <v>149</v>
+      </c>
+      <c r="N17" t="s">
+        <v>33</v>
       </c>
       <c r="O17">
         <v>11</v>
       </c>
       <c r="P17" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q17" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q17">
+        <v>8</v>
+      </c>
+      <c r="R17">
+        <v>1375</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27">
+      <c r="A18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" t="s">
         <v>35</v>
       </c>
-      <c r="R17">
-        <v>8</v>
-      </c>
-      <c r="S17">
-        <v>1375</v>
-      </c>
-      <c r="X17">
-        <v>0</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:28">
-      <c r="A18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" t="s">
-        <v>37</v>
-      </c>
       <c r="E18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J18">
         <v>8</v>
@@ -1580,58 +1527,55 @@
       <c r="K18">
         <v>1.125</v>
       </c>
-      <c r="M18" t="s">
-        <v>34</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
+      <c r="M18">
+        <v>149</v>
+      </c>
+      <c r="N18" t="s">
+        <v>33</v>
       </c>
       <c r="O18">
         <v>14</v>
       </c>
       <c r="P18" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q18" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q18">
+        <v>9</v>
+      </c>
+      <c r="R18">
+        <v>1555.555556</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27">
+      <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" t="s">
         <v>35</v>
       </c>
-      <c r="R18">
-        <v>9</v>
-      </c>
-      <c r="S18">
-        <v>1555.555556</v>
-      </c>
-      <c r="X18">
-        <v>0</v>
-      </c>
-      <c r="Y18">
-        <v>0</v>
-      </c>
-      <c r="Z18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:28">
-      <c r="A19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" t="s">
-        <v>37</v>
-      </c>
       <c r="E19" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J19">
         <v>10</v>
@@ -1639,64 +1583,61 @@
       <c r="K19">
         <v>1.2</v>
       </c>
-      <c r="M19" t="s">
-        <v>34</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
+      <c r="M19">
+        <v>149</v>
+      </c>
+      <c r="N19" t="s">
+        <v>33</v>
       </c>
       <c r="O19">
         <v>17</v>
       </c>
       <c r="P19" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q19">
+        <v>12</v>
       </c>
       <c r="R19">
-        <v>12</v>
-      </c>
-      <c r="S19">
         <v>1416.666667</v>
       </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
       <c r="X19">
         <v>0</v>
       </c>
       <c r="Y19">
         <v>0</v>
       </c>
-      <c r="Z19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:28">
+    </row>
+    <row r="20" spans="1:27">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H20">
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J20">
         <v>11</v>
@@ -1707,67 +1648,64 @@
       <c r="L20">
         <v>12</v>
       </c>
-      <c r="M20" t="s">
-        <v>34</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
+      <c r="M20">
+        <v>149</v>
+      </c>
+      <c r="N20" t="s">
+        <v>33</v>
       </c>
       <c r="O20">
         <v>12</v>
       </c>
       <c r="P20" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q20">
+        <v>11</v>
       </c>
       <c r="R20">
-        <v>11</v>
+        <v>1090.909091</v>
       </c>
       <c r="S20">
-        <v>1090.909091</v>
-      </c>
-      <c r="T20">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="U20">
+        <v>12</v>
       </c>
       <c r="V20">
+        <v>9.090909</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>9.090909</v>
+      </c>
+      <c r="Y20">
         <v>12</v>
       </c>
-      <c r="W20">
-        <v>9.090909</v>
-      </c>
-      <c r="X20">
-        <v>1</v>
-      </c>
-      <c r="Y20">
-        <v>9.090909</v>
-      </c>
-      <c r="Z20">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:28">
+    </row>
+    <row r="21" spans="1:27">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E21" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J21">
         <v>8</v>
@@ -1775,58 +1713,55 @@
       <c r="K21">
         <v>1</v>
       </c>
-      <c r="M21" t="s">
-        <v>34</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
+      <c r="M21">
+        <v>149</v>
+      </c>
+      <c r="N21" t="s">
+        <v>33</v>
       </c>
       <c r="O21">
         <v>8</v>
       </c>
       <c r="P21" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q21">
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>8</v>
-      </c>
-      <c r="S21">
         <v>1000</v>
       </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
       <c r="X21">
         <v>0</v>
       </c>
       <c r="Y21">
         <v>0</v>
       </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:28">
+    </row>
+    <row r="22" spans="1:27">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J22">
         <v>5</v>
@@ -1834,58 +1769,55 @@
       <c r="K22">
         <v>1.2</v>
       </c>
-      <c r="M22" t="s">
-        <v>34</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
+      <c r="M22">
+        <v>149</v>
+      </c>
+      <c r="N22" t="s">
+        <v>33</v>
       </c>
       <c r="O22">
         <v>6</v>
       </c>
       <c r="P22" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q22">
+        <v>6</v>
       </c>
       <c r="R22">
-        <v>6</v>
-      </c>
-      <c r="S22">
         <v>1000</v>
       </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
       <c r="X22">
         <v>0</v>
       </c>
       <c r="Y22">
         <v>0</v>
       </c>
-      <c r="Z22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:28">
+    </row>
+    <row r="23" spans="1:27">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D23" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E23" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J23">
         <v>7</v>
@@ -1893,58 +1825,55 @@
       <c r="K23">
         <v>1</v>
       </c>
-      <c r="M23" t="s">
-        <v>34</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
+      <c r="M23">
+        <v>149</v>
+      </c>
+      <c r="N23" t="s">
+        <v>33</v>
       </c>
       <c r="O23">
         <v>5</v>
       </c>
       <c r="P23" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q23">
+        <v>7</v>
       </c>
       <c r="R23">
-        <v>7</v>
-      </c>
-      <c r="S23">
         <v>714.285714</v>
       </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
       <c r="X23">
         <v>0</v>
       </c>
       <c r="Y23">
         <v>0</v>
       </c>
-      <c r="Z23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:28">
+    </row>
+    <row r="24" spans="1:27">
       <c r="A24" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J24">
         <v>6</v>
@@ -1952,58 +1881,55 @@
       <c r="K24">
         <v>1.166667</v>
       </c>
-      <c r="M24" t="s">
-        <v>34</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
+      <c r="M24">
+        <v>149</v>
+      </c>
+      <c r="N24" t="s">
+        <v>33</v>
       </c>
       <c r="O24">
         <v>4</v>
       </c>
       <c r="P24" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q24">
+        <v>7</v>
       </c>
       <c r="R24">
-        <v>7</v>
-      </c>
-      <c r="S24">
         <v>571.428571</v>
       </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
       <c r="X24">
         <v>0</v>
       </c>
       <c r="Y24">
         <v>0</v>
       </c>
-      <c r="Z24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:28">
+    </row>
+    <row r="25" spans="1:27">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D25" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J25">
         <v>10</v>
@@ -2011,58 +1937,55 @@
       <c r="K25">
         <v>1.4</v>
       </c>
-      <c r="M25" t="s">
-        <v>34</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
+      <c r="M25">
+        <v>149</v>
+      </c>
+      <c r="N25" t="s">
+        <v>33</v>
       </c>
       <c r="O25">
         <v>4</v>
       </c>
       <c r="P25" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q25">
+        <v>14</v>
       </c>
       <c r="R25">
-        <v>14</v>
-      </c>
-      <c r="S25">
         <v>285.714286</v>
       </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
       <c r="X25">
         <v>0</v>
       </c>
       <c r="Y25">
         <v>0</v>
       </c>
-      <c r="Z25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:28">
+    </row>
+    <row r="26" spans="1:27">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J26">
         <v>8</v>
@@ -2070,58 +1993,55 @@
       <c r="K26">
         <v>1</v>
       </c>
-      <c r="M26" t="s">
-        <v>34</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
+      <c r="M26">
+        <v>149</v>
+      </c>
+      <c r="N26" t="s">
+        <v>33</v>
       </c>
       <c r="O26">
         <v>3</v>
       </c>
       <c r="P26" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q26">
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>8</v>
-      </c>
-      <c r="S26">
         <v>375</v>
       </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
       <c r="X26">
         <v>0</v>
       </c>
       <c r="Y26">
         <v>0</v>
       </c>
-      <c r="Z26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:28">
+    </row>
+    <row r="27" spans="1:27">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D27" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E27" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J27">
         <v>14</v>
@@ -2129,58 +2049,55 @@
       <c r="K27">
         <v>1.214286</v>
       </c>
-      <c r="M27" t="s">
-        <v>34</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
+      <c r="M27">
+        <v>149</v>
+      </c>
+      <c r="N27" t="s">
+        <v>33</v>
       </c>
       <c r="O27">
         <v>17</v>
       </c>
       <c r="P27" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q27">
+        <v>17</v>
       </c>
       <c r="R27">
-        <v>17</v>
-      </c>
-      <c r="S27">
         <v>1000</v>
       </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
       <c r="X27">
         <v>0</v>
       </c>
       <c r="Y27">
         <v>0</v>
       </c>
-      <c r="Z27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:28">
+    </row>
+    <row r="28" spans="1:27">
       <c r="A28" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C28" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" t="s">
         <v>29</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>30</v>
       </c>
-      <c r="E28" t="s">
-        <v>31</v>
-      </c>
       <c r="F28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J28">
         <v>5</v>
@@ -2188,58 +2105,55 @@
       <c r="K28">
         <v>1</v>
       </c>
-      <c r="M28" t="s">
-        <v>34</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
+      <c r="M28">
+        <v>149</v>
+      </c>
+      <c r="N28" t="s">
+        <v>33</v>
       </c>
       <c r="O28">
         <v>3</v>
       </c>
       <c r="P28" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q28">
+        <v>5</v>
       </c>
       <c r="R28">
-        <v>5</v>
-      </c>
-      <c r="S28">
         <v>600</v>
       </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
       <c r="X28">
         <v>0</v>
       </c>
       <c r="Y28">
         <v>0</v>
       </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:28">
+    </row>
+    <row r="29" spans="1:27">
       <c r="A29" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" t="s">
         <v>29</v>
       </c>
-      <c r="D29" t="s">
-        <v>30</v>
-      </c>
       <c r="E29" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J29">
         <v>6</v>
@@ -2247,58 +2161,55 @@
       <c r="K29">
         <v>1</v>
       </c>
-      <c r="M29" t="s">
-        <v>34</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
+      <c r="M29">
+        <v>149</v>
+      </c>
+      <c r="N29" t="s">
+        <v>33</v>
       </c>
       <c r="O29">
         <v>5</v>
       </c>
       <c r="P29" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q29" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q29">
+        <v>6</v>
+      </c>
+      <c r="R29">
+        <v>833.333333</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27">
+      <c r="A30" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" t="s">
         <v>35</v>
       </c>
-      <c r="R29">
-        <v>6</v>
-      </c>
-      <c r="S29">
-        <v>833.333333</v>
-      </c>
-      <c r="X29">
-        <v>0</v>
-      </c>
-      <c r="Y29">
-        <v>0</v>
-      </c>
-      <c r="Z29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:28">
-      <c r="A30" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30" t="s">
-        <v>37</v>
-      </c>
       <c r="E30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J30">
         <v>11</v>
@@ -2306,64 +2217,61 @@
       <c r="K30">
         <v>1</v>
       </c>
-      <c r="M30" t="s">
-        <v>34</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
+      <c r="M30">
+        <v>149</v>
+      </c>
+      <c r="N30" t="s">
+        <v>33</v>
       </c>
       <c r="O30">
         <v>9</v>
       </c>
       <c r="P30" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q30" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q30">
+        <v>11</v>
+      </c>
+      <c r="R30">
+        <v>818.181818</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27">
+      <c r="A31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" t="s">
         <v>35</v>
       </c>
-      <c r="R30">
-        <v>11</v>
-      </c>
-      <c r="S30">
-        <v>818.181818</v>
-      </c>
-      <c r="X30">
-        <v>0</v>
-      </c>
-      <c r="Y30">
-        <v>0</v>
-      </c>
-      <c r="Z30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:28">
-      <c r="A31" t="s">
-        <v>45</v>
-      </c>
-      <c r="B31" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" t="s">
-        <v>29</v>
-      </c>
-      <c r="D31" t="s">
-        <v>37</v>
-      </c>
       <c r="E31" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H31">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J31">
         <v>14</v>
@@ -2374,67 +2282,64 @@
       <c r="L31">
         <v>35</v>
       </c>
-      <c r="M31" t="s">
-        <v>34</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
+      <c r="M31">
+        <v>149</v>
+      </c>
+      <c r="N31" t="s">
+        <v>33</v>
       </c>
       <c r="O31">
         <v>35</v>
       </c>
       <c r="P31" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q31" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q31">
+        <v>15</v>
+      </c>
+      <c r="R31">
+        <v>2333.333333</v>
+      </c>
+      <c r="S31">
+        <v>1</v>
+      </c>
+      <c r="U31">
         <v>35</v>
       </c>
-      <c r="R31">
-        <v>15</v>
-      </c>
-      <c r="S31">
-        <v>2333.333333</v>
-      </c>
-      <c r="T31">
-        <v>1</v>
-      </c>
       <c r="V31">
+        <v>6.666667</v>
+      </c>
+      <c r="W31">
+        <v>1</v>
+      </c>
+      <c r="X31">
+        <v>6.666667</v>
+      </c>
+      <c r="Y31">
         <v>35</v>
       </c>
-      <c r="W31">
-        <v>6.666667</v>
-      </c>
-      <c r="X31">
-        <v>1</v>
-      </c>
-      <c r="Y31">
-        <v>6.666667</v>
-      </c>
-      <c r="Z31">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:28">
+    </row>
+    <row r="32" spans="1:27">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D32" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J32">
         <v>13</v>
@@ -2442,58 +2347,55 @@
       <c r="K32">
         <v>1</v>
       </c>
-      <c r="M32" t="s">
-        <v>34</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
+      <c r="M32">
+        <v>149</v>
+      </c>
+      <c r="N32" t="s">
+        <v>33</v>
       </c>
       <c r="O32">
         <v>13</v>
       </c>
       <c r="P32" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q32">
+        <v>13</v>
       </c>
       <c r="R32">
-        <v>13</v>
-      </c>
-      <c r="S32">
         <v>1000</v>
       </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
       <c r="X32">
         <v>0</v>
       </c>
       <c r="Y32">
         <v>0</v>
       </c>
-      <c r="Z32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:28">
+    </row>
+    <row r="33" spans="1:27">
       <c r="A33" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D33" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J33">
         <v>18</v>
@@ -2501,58 +2403,55 @@
       <c r="K33">
         <v>1</v>
       </c>
-      <c r="M33" t="s">
-        <v>34</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
+      <c r="M33">
+        <v>149</v>
+      </c>
+      <c r="N33" t="s">
+        <v>33</v>
       </c>
       <c r="O33">
         <v>17</v>
       </c>
       <c r="P33" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q33">
+        <v>18</v>
       </c>
       <c r="R33">
-        <v>18</v>
-      </c>
-      <c r="S33">
         <v>944.444444</v>
       </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
       <c r="X33">
         <v>0</v>
       </c>
       <c r="Y33">
         <v>0</v>
       </c>
-      <c r="Z33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:28">
+    </row>
+    <row r="34" spans="1:27">
       <c r="A34" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D34" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J34">
         <v>7</v>
@@ -2560,64 +2459,61 @@
       <c r="K34">
         <v>1</v>
       </c>
-      <c r="M34" t="s">
-        <v>34</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
+      <c r="M34">
+        <v>149</v>
+      </c>
+      <c r="N34" t="s">
+        <v>33</v>
       </c>
       <c r="O34">
         <v>8</v>
       </c>
       <c r="P34" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q34">
+        <v>7</v>
       </c>
       <c r="R34">
-        <v>7</v>
-      </c>
-      <c r="S34">
         <v>1142.857143</v>
       </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
       <c r="X34">
         <v>0</v>
       </c>
       <c r="Y34">
         <v>0</v>
       </c>
-      <c r="Z34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:28">
+    </row>
+    <row r="35" spans="1:27">
       <c r="A35" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D35" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E35" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H35">
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J35">
         <v>16</v>
@@ -2628,126 +2524,120 @@
       <c r="L35">
         <v>39</v>
       </c>
-      <c r="M35" t="s">
-        <v>34</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
+      <c r="M35">
+        <v>149</v>
+      </c>
+      <c r="N35" t="s">
+        <v>33</v>
       </c>
       <c r="O35">
         <v>39</v>
       </c>
       <c r="P35" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q35">
+        <v>17</v>
       </c>
       <c r="R35">
-        <v>17</v>
+        <v>2294.117647</v>
       </c>
       <c r="S35">
-        <v>2294.117647</v>
-      </c>
-      <c r="T35">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="U35">
+        <v>39</v>
       </c>
       <c r="V35">
+        <v>5.882353</v>
+      </c>
+      <c r="W35">
+        <v>1</v>
+      </c>
+      <c r="X35">
+        <v>5.882353</v>
+      </c>
+      <c r="Y35">
         <v>39</v>
       </c>
-      <c r="W35">
-        <v>5.882353</v>
-      </c>
-      <c r="X35">
-        <v>1</v>
-      </c>
-      <c r="Y35">
-        <v>5.882353</v>
-      </c>
-      <c r="Z35">
+    </row>
+    <row r="36" spans="1:27">
+      <c r="A36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="36" spans="1:28">
-      <c r="A36" t="s">
-        <v>45</v>
-      </c>
-      <c r="B36" t="s">
-        <v>45</v>
-      </c>
-      <c r="C36" t="s">
-        <v>29</v>
-      </c>
-      <c r="D36" t="s">
-        <v>41</v>
-      </c>
       <c r="E36" t="s">
+        <v>37</v>
+      </c>
+      <c r="F36" t="s">
+        <v>31</v>
+      </c>
+      <c r="G36" t="s">
+        <v>32</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+      <c r="K36">
+        <v>1</v>
+      </c>
+      <c r="M36">
+        <v>149</v>
+      </c>
+      <c r="N36" t="s">
+        <v>33</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q36">
+        <v>1</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27">
+      <c r="A37" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" t="s">
+        <v>28</v>
+      </c>
+      <c r="D37" t="s">
         <v>39</v>
       </c>
-      <c r="F36" t="s">
-        <v>32</v>
-      </c>
-      <c r="G36" t="s">
-        <v>33</v>
-      </c>
-      <c r="J36">
-        <v>1</v>
-      </c>
-      <c r="K36">
-        <v>1</v>
-      </c>
-      <c r="M36" t="s">
-        <v>34</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="P36" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>35</v>
-      </c>
-      <c r="R36">
-        <v>1</v>
-      </c>
-      <c r="S36">
-        <v>0</v>
-      </c>
-      <c r="X36">
-        <v>0</v>
-      </c>
-      <c r="Y36">
-        <v>0</v>
-      </c>
-      <c r="Z36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:28">
-      <c r="A37" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" t="s">
-        <v>45</v>
-      </c>
-      <c r="C37" t="s">
-        <v>29</v>
-      </c>
-      <c r="D37" t="s">
-        <v>41</v>
-      </c>
       <c r="E37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J37">
         <v>9</v>
@@ -2755,58 +2645,55 @@
       <c r="K37">
         <v>1</v>
       </c>
-      <c r="M37" t="s">
-        <v>34</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
+      <c r="M37">
+        <v>149</v>
+      </c>
+      <c r="N37" t="s">
+        <v>33</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q37">
+        <v>9</v>
       </c>
       <c r="R37">
-        <v>9</v>
-      </c>
-      <c r="S37">
         <v>666.666667</v>
       </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
       <c r="X37">
         <v>0</v>
       </c>
       <c r="Y37">
         <v>0</v>
       </c>
-      <c r="Z37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:28">
+    </row>
+    <row r="38" spans="1:27">
       <c r="A38" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D38" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E38" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J38">
         <v>21</v>
@@ -2814,64 +2701,61 @@
       <c r="K38">
         <v>1</v>
       </c>
-      <c r="M38" t="s">
-        <v>34</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
+      <c r="M38">
+        <v>149</v>
+      </c>
+      <c r="N38" t="s">
+        <v>33</v>
       </c>
       <c r="O38">
         <v>12</v>
       </c>
       <c r="P38" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q38">
+        <v>21</v>
       </c>
       <c r="R38">
-        <v>21</v>
-      </c>
-      <c r="S38">
         <v>571.428571</v>
       </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
       <c r="X38">
         <v>0</v>
       </c>
       <c r="Y38">
         <v>0</v>
       </c>
-      <c r="Z38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:28">
+    </row>
+    <row r="39" spans="1:27">
       <c r="A39" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D39" t="s">
+        <v>40</v>
+      </c>
+      <c r="E39" t="s">
+        <v>30</v>
+      </c>
+      <c r="F39" t="s">
+        <v>31</v>
+      </c>
+      <c r="G39" t="s">
+        <v>32</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39" t="s">
         <v>42</v>
-      </c>
-      <c r="E39" t="s">
-        <v>31</v>
-      </c>
-      <c r="F39" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" t="s">
-        <v>33</v>
-      </c>
-      <c r="H39">
-        <v>1</v>
-      </c>
-      <c r="I39" t="s">
-        <v>44</v>
       </c>
       <c r="J39">
         <v>13</v>
@@ -2882,67 +2766,64 @@
       <c r="L39">
         <v>11</v>
       </c>
-      <c r="M39" t="s">
-        <v>34</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
+      <c r="M39">
+        <v>149</v>
+      </c>
+      <c r="N39" t="s">
+        <v>33</v>
       </c>
       <c r="O39">
         <v>11</v>
       </c>
       <c r="P39" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q39">
+        <v>14</v>
       </c>
       <c r="R39">
-        <v>14</v>
+        <v>785.714286</v>
       </c>
       <c r="S39">
-        <v>785.714286</v>
-      </c>
-      <c r="T39">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="U39">
+        <v>11</v>
       </c>
       <c r="V39">
+        <v>7.142857</v>
+      </c>
+      <c r="W39">
+        <v>1</v>
+      </c>
+      <c r="X39">
+        <v>7.142857</v>
+      </c>
+      <c r="Y39">
         <v>11</v>
       </c>
-      <c r="W39">
-        <v>7.142857</v>
-      </c>
-      <c r="X39">
-        <v>1</v>
-      </c>
-      <c r="Y39">
-        <v>7.142857</v>
-      </c>
-      <c r="Z39">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:28">
+    </row>
+    <row r="40" spans="1:27">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D40" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E40" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J40">
         <v>16</v>
@@ -2950,58 +2831,55 @@
       <c r="K40">
         <v>1.0625</v>
       </c>
-      <c r="M40" t="s">
-        <v>34</v>
-      </c>
-      <c r="N40">
-        <v>0</v>
+      <c r="M40">
+        <v>149</v>
+      </c>
+      <c r="N40" t="s">
+        <v>33</v>
       </c>
       <c r="O40">
         <v>6</v>
       </c>
       <c r="P40" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q40">
+        <v>17</v>
       </c>
       <c r="R40">
-        <v>17</v>
-      </c>
-      <c r="S40">
         <v>352.941176</v>
       </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
       <c r="X40">
         <v>0</v>
       </c>
       <c r="Y40">
         <v>0</v>
       </c>
-      <c r="Z40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:28">
+    </row>
+    <row r="41" spans="1:27">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B41" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C41" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" t="s">
         <v>29</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>30</v>
       </c>
-      <c r="E41" t="s">
-        <v>31</v>
-      </c>
       <c r="F41" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J41">
         <v>7</v>
@@ -3009,64 +2887,61 @@
       <c r="K41">
         <v>1.428571</v>
       </c>
-      <c r="M41" t="s">
-        <v>34</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
+      <c r="M41">
+        <v>149</v>
+      </c>
+      <c r="N41" t="s">
+        <v>33</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q41">
+        <v>10</v>
       </c>
       <c r="R41">
-        <v>10</v>
-      </c>
-      <c r="S41">
         <v>600</v>
       </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
       <c r="X41">
         <v>0</v>
       </c>
       <c r="Y41">
         <v>0</v>
       </c>
-      <c r="Z41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:28">
+    </row>
+    <row r="42" spans="1:27">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C42" t="s">
+        <v>28</v>
+      </c>
+      <c r="D42" t="s">
         <v>29</v>
       </c>
-      <c r="D42" t="s">
-        <v>30</v>
-      </c>
       <c r="E42" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H42">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J42">
         <v>7</v>
@@ -3077,67 +2952,64 @@
       <c r="L42">
         <v>27</v>
       </c>
-      <c r="M42" t="s">
-        <v>34</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
+      <c r="M42">
+        <v>149</v>
+      </c>
+      <c r="N42" t="s">
+        <v>33</v>
       </c>
       <c r="O42">
         <v>27</v>
       </c>
       <c r="P42" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q42" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q42">
+        <v>8</v>
+      </c>
+      <c r="R42">
+        <v>3375</v>
+      </c>
+      <c r="S42">
+        <v>1</v>
+      </c>
+      <c r="U42">
+        <v>27</v>
+      </c>
+      <c r="V42">
+        <v>12.5</v>
+      </c>
+      <c r="W42">
+        <v>1</v>
+      </c>
+      <c r="X42">
+        <v>12.5</v>
+      </c>
+      <c r="Y42">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27">
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" t="s">
+        <v>28</v>
+      </c>
+      <c r="D43" t="s">
         <v>35</v>
       </c>
-      <c r="R42">
-        <v>8</v>
-      </c>
-      <c r="S42">
-        <v>3375</v>
-      </c>
-      <c r="T42">
-        <v>1</v>
-      </c>
-      <c r="V42">
-        <v>27</v>
-      </c>
-      <c r="W42">
-        <v>12.5</v>
-      </c>
-      <c r="X42">
-        <v>1</v>
-      </c>
-      <c r="Y42">
-        <v>12.5</v>
-      </c>
-      <c r="Z42">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="43" spans="1:28">
-      <c r="A43" t="s">
-        <v>46</v>
-      </c>
-      <c r="B43" t="s">
-        <v>46</v>
-      </c>
-      <c r="C43" t="s">
-        <v>29</v>
-      </c>
-      <c r="D43" t="s">
-        <v>37</v>
-      </c>
       <c r="E43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J43">
         <v>11</v>
@@ -3145,64 +3017,61 @@
       <c r="K43">
         <v>1</v>
       </c>
-      <c r="M43" t="s">
-        <v>34</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
+      <c r="M43">
+        <v>149</v>
+      </c>
+      <c r="N43" t="s">
+        <v>33</v>
       </c>
       <c r="O43">
         <v>14</v>
       </c>
       <c r="P43" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q43" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q43">
+        <v>11</v>
+      </c>
+      <c r="R43">
+        <v>1272.727273</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" t="s">
+        <v>28</v>
+      </c>
+      <c r="D44" t="s">
         <v>35</v>
       </c>
-      <c r="R43">
-        <v>11</v>
-      </c>
-      <c r="S43">
-        <v>1272.727273</v>
-      </c>
-      <c r="X43">
-        <v>0</v>
-      </c>
-      <c r="Y43">
-        <v>0</v>
-      </c>
-      <c r="Z43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:28">
-      <c r="A44" t="s">
-        <v>46</v>
-      </c>
-      <c r="B44" t="s">
-        <v>46</v>
-      </c>
-      <c r="C44" t="s">
-        <v>29</v>
-      </c>
-      <c r="D44" t="s">
-        <v>37</v>
-      </c>
       <c r="E44" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H44">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J44">
         <v>12</v>
@@ -3213,67 +3082,64 @@
       <c r="L44">
         <v>19</v>
       </c>
-      <c r="M44" t="s">
-        <v>34</v>
-      </c>
-      <c r="N44">
-        <v>0</v>
+      <c r="M44">
+        <v>149</v>
+      </c>
+      <c r="N44" t="s">
+        <v>33</v>
       </c>
       <c r="O44">
         <v>19</v>
       </c>
       <c r="P44" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q44">
+        <v>13</v>
       </c>
       <c r="R44">
-        <v>13</v>
+        <v>1461.538462</v>
       </c>
       <c r="S44">
-        <v>1461.538462</v>
-      </c>
-      <c r="T44">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="U44">
+        <v>19</v>
       </c>
       <c r="V44">
+        <v>7.692308</v>
+      </c>
+      <c r="W44">
+        <v>1</v>
+      </c>
+      <c r="X44">
+        <v>7.692308</v>
+      </c>
+      <c r="Y44">
         <v>19</v>
       </c>
-      <c r="W44">
-        <v>7.692308</v>
-      </c>
-      <c r="X44">
-        <v>1</v>
-      </c>
-      <c r="Y44">
-        <v>7.692308</v>
-      </c>
-      <c r="Z44">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="45" spans="1:28">
+    </row>
+    <row r="45" spans="1:27">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D45" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E45" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G45" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J45">
         <v>1</v>
@@ -3281,58 +3147,55 @@
       <c r="K45">
         <v>1</v>
       </c>
-      <c r="M45" t="s">
-        <v>34</v>
-      </c>
-      <c r="N45">
-        <v>0</v>
+      <c r="M45">
+        <v>149</v>
+      </c>
+      <c r="N45" t="s">
+        <v>33</v>
       </c>
       <c r="O45">
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q45">
+        <v>1</v>
       </c>
       <c r="R45">
-        <v>1</v>
-      </c>
-      <c r="S45">
         <v>1000</v>
       </c>
+      <c r="W45">
+        <v>0</v>
+      </c>
       <c r="X45">
         <v>0</v>
       </c>
       <c r="Y45">
         <v>0</v>
       </c>
-      <c r="Z45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:28">
+    </row>
+    <row r="46" spans="1:27">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D46" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G46" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J46">
         <v>17</v>
@@ -3340,58 +3203,55 @@
       <c r="K46">
         <v>1.117647</v>
       </c>
-      <c r="M46" t="s">
-        <v>34</v>
-      </c>
-      <c r="N46">
-        <v>0</v>
+      <c r="M46">
+        <v>149</v>
+      </c>
+      <c r="N46" t="s">
+        <v>33</v>
       </c>
       <c r="O46">
         <v>24</v>
       </c>
       <c r="P46" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q46">
+        <v>19</v>
       </c>
       <c r="R46">
-        <v>19</v>
-      </c>
-      <c r="S46">
         <v>1263.157895</v>
       </c>
+      <c r="W46">
+        <v>0</v>
+      </c>
       <c r="X46">
         <v>0</v>
       </c>
       <c r="Y46">
         <v>0</v>
       </c>
-      <c r="Z46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:28">
+    </row>
+    <row r="47" spans="1:27">
       <c r="A47" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C47" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D47" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E47" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J47">
         <v>14</v>
@@ -3399,58 +3259,55 @@
       <c r="K47">
         <v>1</v>
       </c>
-      <c r="M47" t="s">
-        <v>34</v>
-      </c>
-      <c r="N47">
-        <v>0</v>
+      <c r="M47">
+        <v>149</v>
+      </c>
+      <c r="N47" t="s">
+        <v>33</v>
       </c>
       <c r="O47">
         <v>13</v>
       </c>
       <c r="P47" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q47">
+        <v>14</v>
       </c>
       <c r="R47">
-        <v>14</v>
-      </c>
-      <c r="S47">
         <v>928.571429</v>
       </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
       <c r="X47">
         <v>0</v>
       </c>
       <c r="Y47">
         <v>0</v>
       </c>
-      <c r="Z47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:28">
+    </row>
+    <row r="48" spans="1:27">
       <c r="A48" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D48" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J48">
         <v>12</v>
@@ -3458,58 +3315,55 @@
       <c r="K48">
         <v>1</v>
       </c>
-      <c r="M48" t="s">
-        <v>34</v>
-      </c>
-      <c r="N48">
-        <v>0</v>
+      <c r="M48">
+        <v>149</v>
+      </c>
+      <c r="N48" t="s">
+        <v>33</v>
       </c>
       <c r="O48">
         <v>7</v>
       </c>
       <c r="P48" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q48">
+        <v>12</v>
       </c>
       <c r="R48">
-        <v>12</v>
-      </c>
-      <c r="S48">
         <v>583.333333</v>
       </c>
+      <c r="W48">
+        <v>0</v>
+      </c>
       <c r="X48">
         <v>0</v>
       </c>
       <c r="Y48">
         <v>0</v>
       </c>
-      <c r="Z48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:28">
+    </row>
+    <row r="49" spans="1:27">
       <c r="A49" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B49" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C49" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D49" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E49" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J49">
         <v>10</v>
@@ -3517,58 +3371,55 @@
       <c r="K49">
         <v>1.2</v>
       </c>
-      <c r="M49" t="s">
-        <v>34</v>
-      </c>
-      <c r="N49">
-        <v>0</v>
+      <c r="M49">
+        <v>149</v>
+      </c>
+      <c r="N49" t="s">
+        <v>33</v>
       </c>
       <c r="O49">
         <v>18</v>
       </c>
       <c r="P49" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q49">
+        <v>12</v>
       </c>
       <c r="R49">
-        <v>12</v>
-      </c>
-      <c r="S49">
         <v>1500</v>
       </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
       <c r="X49">
         <v>0</v>
       </c>
       <c r="Y49">
         <v>0</v>
       </c>
-      <c r="Z49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:28">
+    </row>
+    <row r="50" spans="1:27">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B50" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C50" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D50" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E50" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F50" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -3576,25 +3427,25 @@
       <c r="K50">
         <v>2</v>
       </c>
-      <c r="M50" t="s">
-        <v>34</v>
-      </c>
-      <c r="N50">
-        <v>0</v>
+      <c r="M50">
+        <v>149</v>
+      </c>
+      <c r="N50" t="s">
+        <v>33</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q50">
+        <v>2</v>
       </c>
       <c r="R50">
-        <v>2</v>
-      </c>
-      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="W50">
         <v>0</v>
       </c>
       <c r="X50">
@@ -3603,31 +3454,28 @@
       <c r="Y50">
         <v>0</v>
       </c>
-      <c r="Z50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:28">
+    </row>
+    <row r="51" spans="1:27">
       <c r="A51" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B51" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D51" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G51" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J51">
         <v>9</v>
@@ -3635,58 +3483,55 @@
       <c r="K51">
         <v>1.111111</v>
       </c>
-      <c r="M51" t="s">
-        <v>34</v>
-      </c>
-      <c r="N51">
-        <v>0</v>
+      <c r="M51">
+        <v>149</v>
+      </c>
+      <c r="N51" t="s">
+        <v>33</v>
       </c>
       <c r="O51">
         <v>8</v>
       </c>
       <c r="P51" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q51">
+        <v>10</v>
       </c>
       <c r="R51">
-        <v>10</v>
-      </c>
-      <c r="S51">
         <v>800</v>
       </c>
+      <c r="W51">
+        <v>0</v>
+      </c>
       <c r="X51">
         <v>0</v>
       </c>
       <c r="Y51">
         <v>0</v>
       </c>
-      <c r="Z51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:28">
+    </row>
+    <row r="52" spans="1:27">
       <c r="A52" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B52" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C52" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D52" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E52" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F52" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G52" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J52">
         <v>9</v>
@@ -3694,58 +3539,55 @@
       <c r="K52">
         <v>1.333333</v>
       </c>
-      <c r="M52" t="s">
-        <v>34</v>
-      </c>
-      <c r="N52">
-        <v>0</v>
+      <c r="M52">
+        <v>149</v>
+      </c>
+      <c r="N52" t="s">
+        <v>33</v>
       </c>
       <c r="O52">
         <v>8</v>
       </c>
       <c r="P52" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q52">
+        <v>12</v>
       </c>
       <c r="R52">
-        <v>12</v>
-      </c>
-      <c r="S52">
         <v>666.666667</v>
       </c>
+      <c r="W52">
+        <v>0</v>
+      </c>
       <c r="X52">
         <v>0</v>
       </c>
       <c r="Y52">
         <v>0</v>
       </c>
-      <c r="Z52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:28">
+    </row>
+    <row r="53" spans="1:27">
       <c r="A53" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B53" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C53" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D53" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F53" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G53" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J53">
         <v>12</v>
@@ -3753,58 +3595,55 @@
       <c r="K53">
         <v>1</v>
       </c>
-      <c r="M53" t="s">
-        <v>34</v>
-      </c>
-      <c r="N53">
-        <v>0</v>
+      <c r="M53">
+        <v>149</v>
+      </c>
+      <c r="N53" t="s">
+        <v>33</v>
       </c>
       <c r="O53">
         <v>10</v>
       </c>
       <c r="P53" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q53">
+        <v>12</v>
       </c>
       <c r="R53">
-        <v>12</v>
-      </c>
-      <c r="S53">
         <v>833.333333</v>
       </c>
+      <c r="W53">
+        <v>0</v>
+      </c>
       <c r="X53">
         <v>0</v>
       </c>
       <c r="Y53">
         <v>0</v>
       </c>
-      <c r="Z53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:28">
+    </row>
+    <row r="54" spans="1:27">
       <c r="A54" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B54" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C54" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D54" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E54" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G54" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J54">
         <v>19</v>
@@ -3812,58 +3651,55 @@
       <c r="K54">
         <v>1.105263</v>
       </c>
-      <c r="M54" t="s">
-        <v>34</v>
-      </c>
-      <c r="N54">
-        <v>0</v>
+      <c r="M54">
+        <v>149</v>
+      </c>
+      <c r="N54" t="s">
+        <v>33</v>
       </c>
       <c r="O54">
         <v>8</v>
       </c>
       <c r="P54" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q54">
+        <v>21</v>
       </c>
       <c r="R54">
-        <v>21</v>
-      </c>
-      <c r="S54">
         <v>380.952381</v>
       </c>
+      <c r="W54">
+        <v>0</v>
+      </c>
       <c r="X54">
         <v>0</v>
       </c>
       <c r="Y54">
         <v>0</v>
       </c>
-      <c r="Z54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:28">
+    </row>
+    <row r="55" spans="1:27">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B55" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C55" t="s">
+        <v>28</v>
+      </c>
+      <c r="D55" t="s">
         <v>29</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>30</v>
       </c>
-      <c r="E55" t="s">
-        <v>31</v>
-      </c>
       <c r="F55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G55" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J55">
         <v>2</v>
@@ -3871,58 +3707,55 @@
       <c r="K55">
         <v>1</v>
       </c>
-      <c r="M55" t="s">
+      <c r="M55">
+        <v>149</v>
+      </c>
+      <c r="N55" t="s">
+        <v>33</v>
+      </c>
+      <c r="O55">
+        <v>1</v>
+      </c>
+      <c r="P55" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q55">
+        <v>2</v>
+      </c>
+      <c r="R55">
+        <v>500</v>
+      </c>
+      <c r="W55">
+        <v>0</v>
+      </c>
+      <c r="X55">
+        <v>0</v>
+      </c>
+      <c r="Y55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:27">
+      <c r="A56" t="s">
+        <v>45</v>
+      </c>
+      <c r="B56" t="s">
+        <v>45</v>
+      </c>
+      <c r="C56" t="s">
+        <v>28</v>
+      </c>
+      <c r="D56" t="s">
+        <v>29</v>
+      </c>
+      <c r="E56" t="s">
         <v>34</v>
       </c>
-      <c r="N55">
-        <v>0</v>
-      </c>
-      <c r="O55">
-        <v>1</v>
-      </c>
-      <c r="P55" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>35</v>
-      </c>
-      <c r="R55">
-        <v>2</v>
-      </c>
-      <c r="S55">
-        <v>500</v>
-      </c>
-      <c r="X55">
-        <v>0</v>
-      </c>
-      <c r="Y55">
-        <v>0</v>
-      </c>
-      <c r="Z55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:28">
-      <c r="A56" t="s">
-        <v>47</v>
-      </c>
-      <c r="B56" t="s">
-        <v>47</v>
-      </c>
-      <c r="C56" t="s">
-        <v>29</v>
-      </c>
-      <c r="D56" t="s">
-        <v>30</v>
-      </c>
-      <c r="E56" t="s">
-        <v>36</v>
-      </c>
       <c r="F56" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G56" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J56">
         <v>5</v>
@@ -3930,58 +3763,55 @@
       <c r="K56">
         <v>1.2</v>
       </c>
-      <c r="M56" t="s">
-        <v>34</v>
-      </c>
-      <c r="N56">
-        <v>0</v>
+      <c r="M56">
+        <v>149</v>
+      </c>
+      <c r="N56" t="s">
+        <v>33</v>
       </c>
       <c r="O56">
         <v>4</v>
       </c>
       <c r="P56" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q56" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q56">
+        <v>6</v>
+      </c>
+      <c r="R56">
+        <v>666.666667</v>
+      </c>
+      <c r="W56">
+        <v>0</v>
+      </c>
+      <c r="X56">
+        <v>0</v>
+      </c>
+      <c r="Y56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:27">
+      <c r="A57" t="s">
+        <v>45</v>
+      </c>
+      <c r="B57" t="s">
+        <v>45</v>
+      </c>
+      <c r="C57" t="s">
+        <v>28</v>
+      </c>
+      <c r="D57" t="s">
         <v>35</v>
       </c>
-      <c r="R56">
-        <v>6</v>
-      </c>
-      <c r="S56">
-        <v>666.666667</v>
-      </c>
-      <c r="X56">
-        <v>0</v>
-      </c>
-      <c r="Y56">
-        <v>0</v>
-      </c>
-      <c r="Z56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:28">
-      <c r="A57" t="s">
-        <v>47</v>
-      </c>
-      <c r="B57" t="s">
-        <v>47</v>
-      </c>
-      <c r="C57" t="s">
-        <v>29</v>
-      </c>
-      <c r="D57" t="s">
-        <v>37</v>
-      </c>
       <c r="E57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F57" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G57" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J57">
         <v>14</v>
@@ -3989,58 +3819,55 @@
       <c r="K57">
         <v>1.142857</v>
       </c>
-      <c r="M57" t="s">
-        <v>34</v>
-      </c>
-      <c r="N57">
-        <v>0</v>
+      <c r="M57">
+        <v>149</v>
+      </c>
+      <c r="N57" t="s">
+        <v>33</v>
       </c>
       <c r="O57">
         <v>14</v>
       </c>
       <c r="P57" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q57" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q57">
+        <v>16</v>
+      </c>
+      <c r="R57">
+        <v>875</v>
+      </c>
+      <c r="W57">
+        <v>0</v>
+      </c>
+      <c r="X57">
+        <v>0</v>
+      </c>
+      <c r="Y57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:27">
+      <c r="A58" t="s">
+        <v>45</v>
+      </c>
+      <c r="B58" t="s">
+        <v>45</v>
+      </c>
+      <c r="C58" t="s">
+        <v>28</v>
+      </c>
+      <c r="D58" t="s">
         <v>35</v>
       </c>
-      <c r="R57">
-        <v>16</v>
-      </c>
-      <c r="S57">
-        <v>875</v>
-      </c>
-      <c r="X57">
-        <v>0</v>
-      </c>
-      <c r="Y57">
-        <v>0</v>
-      </c>
-      <c r="Z57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:28">
-      <c r="A58" t="s">
-        <v>47</v>
-      </c>
-      <c r="B58" t="s">
-        <v>47</v>
-      </c>
-      <c r="C58" t="s">
-        <v>29</v>
-      </c>
-      <c r="D58" t="s">
-        <v>37</v>
-      </c>
       <c r="E58" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F58" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G58" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J58">
         <v>11</v>
@@ -4048,64 +3875,61 @@
       <c r="K58">
         <v>1</v>
       </c>
-      <c r="M58" t="s">
-        <v>34</v>
-      </c>
-      <c r="N58">
-        <v>0</v>
+      <c r="M58">
+        <v>149</v>
+      </c>
+      <c r="N58" t="s">
+        <v>33</v>
       </c>
       <c r="O58">
         <v>16</v>
       </c>
       <c r="P58" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q58">
+        <v>11</v>
       </c>
       <c r="R58">
-        <v>11</v>
-      </c>
-      <c r="S58">
         <v>1454.545455</v>
       </c>
+      <c r="W58">
+        <v>0</v>
+      </c>
       <c r="X58">
         <v>0</v>
       </c>
       <c r="Y58">
         <v>0</v>
       </c>
-      <c r="Z58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:28">
+    </row>
+    <row r="59" spans="1:27">
       <c r="A59" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B59" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C59" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D59" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H59">
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J59">
         <v>11</v>
@@ -4116,67 +3940,64 @@
       <c r="L59">
         <v>22</v>
       </c>
-      <c r="M59" t="s">
-        <v>34</v>
-      </c>
-      <c r="N59">
-        <v>0</v>
+      <c r="M59">
+        <v>149</v>
+      </c>
+      <c r="N59" t="s">
+        <v>33</v>
       </c>
       <c r="O59">
         <v>22</v>
       </c>
       <c r="P59" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q59" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q59">
+        <v>11</v>
       </c>
       <c r="R59">
-        <v>11</v>
+        <v>2000</v>
       </c>
       <c r="S59">
-        <v>2000</v>
-      </c>
-      <c r="T59">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="U59">
+        <v>22</v>
       </c>
       <c r="V59">
+        <v>9.090909</v>
+      </c>
+      <c r="W59">
+        <v>1</v>
+      </c>
+      <c r="X59">
+        <v>9.090909</v>
+      </c>
+      <c r="Y59">
         <v>22</v>
       </c>
-      <c r="W59">
-        <v>9.090909</v>
-      </c>
-      <c r="X59">
-        <v>1</v>
-      </c>
-      <c r="Y59">
-        <v>9.090909</v>
-      </c>
-      <c r="Z59">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="60" spans="1:28">
+    </row>
+    <row r="60" spans="1:27">
       <c r="A60" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B60" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C60" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D60" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E60" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F60" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G60" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J60">
         <v>18</v>
@@ -4184,58 +4005,55 @@
       <c r="K60">
         <v>1.055556</v>
       </c>
-      <c r="M60" t="s">
-        <v>34</v>
-      </c>
-      <c r="N60">
-        <v>0</v>
+      <c r="M60">
+        <v>149</v>
+      </c>
+      <c r="N60" t="s">
+        <v>33</v>
       </c>
       <c r="O60">
         <v>20</v>
       </c>
       <c r="P60" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q60" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q60">
+        <v>19</v>
       </c>
       <c r="R60">
-        <v>19</v>
-      </c>
-      <c r="S60">
         <v>1052.631579</v>
       </c>
+      <c r="W60">
+        <v>0</v>
+      </c>
       <c r="X60">
         <v>0</v>
       </c>
       <c r="Y60">
         <v>0</v>
       </c>
-      <c r="Z60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:28">
+    </row>
+    <row r="61" spans="1:27">
       <c r="A61" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B61" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C61" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D61" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E61" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F61" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G61" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J61">
         <v>8</v>
@@ -4243,58 +4061,55 @@
       <c r="K61">
         <v>1</v>
       </c>
-      <c r="M61" t="s">
-        <v>34</v>
-      </c>
-      <c r="N61">
-        <v>0</v>
+      <c r="M61">
+        <v>149</v>
+      </c>
+      <c r="N61" t="s">
+        <v>33</v>
       </c>
       <c r="O61">
         <v>5</v>
       </c>
       <c r="P61" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q61">
+        <v>8</v>
       </c>
       <c r="R61">
-        <v>8</v>
-      </c>
-      <c r="S61">
         <v>625</v>
       </c>
+      <c r="W61">
+        <v>0</v>
+      </c>
       <c r="X61">
         <v>0</v>
       </c>
       <c r="Y61">
         <v>0</v>
       </c>
-      <c r="Z61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:28">
+    </row>
+    <row r="62" spans="1:27">
       <c r="A62" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B62" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C62" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D62" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E62" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F62" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G62" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J62">
         <v>12</v>
@@ -4302,58 +4117,55 @@
       <c r="K62">
         <v>1.166667</v>
       </c>
-      <c r="M62" t="s">
-        <v>34</v>
-      </c>
-      <c r="N62">
-        <v>0</v>
+      <c r="M62">
+        <v>149</v>
+      </c>
+      <c r="N62" t="s">
+        <v>33</v>
       </c>
       <c r="O62">
         <v>17</v>
       </c>
       <c r="P62" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q62" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q62">
+        <v>14</v>
       </c>
       <c r="R62">
-        <v>14</v>
-      </c>
-      <c r="S62">
         <v>1214.285714</v>
       </c>
+      <c r="W62">
+        <v>0</v>
+      </c>
       <c r="X62">
         <v>0</v>
       </c>
       <c r="Y62">
         <v>0</v>
       </c>
-      <c r="Z62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:28">
+    </row>
+    <row r="63" spans="1:27">
       <c r="A63" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B63" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C63" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D63" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E63" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F63" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G63" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J63">
         <v>15</v>
@@ -4361,58 +4173,55 @@
       <c r="K63">
         <v>1.066667</v>
       </c>
-      <c r="M63" t="s">
-        <v>34</v>
-      </c>
-      <c r="N63">
-        <v>0</v>
+      <c r="M63">
+        <v>149</v>
+      </c>
+      <c r="N63" t="s">
+        <v>33</v>
       </c>
       <c r="O63">
         <v>14</v>
       </c>
       <c r="P63" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q63" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q63">
+        <v>16</v>
       </c>
       <c r="R63">
-        <v>16</v>
-      </c>
-      <c r="S63">
         <v>875</v>
       </c>
+      <c r="W63">
+        <v>0</v>
+      </c>
       <c r="X63">
         <v>0</v>
       </c>
       <c r="Y63">
         <v>0</v>
       </c>
-      <c r="Z63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:28">
+    </row>
+    <row r="64" spans="1:27">
       <c r="A64" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B64" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C64" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D64" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E64" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F64" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G64" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J64">
         <v>16</v>
@@ -4420,58 +4229,55 @@
       <c r="K64">
         <v>1.1875</v>
       </c>
-      <c r="M64" t="s">
-        <v>34</v>
-      </c>
-      <c r="N64">
-        <v>0</v>
+      <c r="M64">
+        <v>149</v>
+      </c>
+      <c r="N64" t="s">
+        <v>33</v>
       </c>
       <c r="O64">
         <v>21</v>
       </c>
       <c r="P64" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q64">
+        <v>19</v>
       </c>
       <c r="R64">
-        <v>19</v>
-      </c>
-      <c r="S64">
         <v>1105.263158</v>
       </c>
+      <c r="W64">
+        <v>0</v>
+      </c>
       <c r="X64">
         <v>0</v>
       </c>
       <c r="Y64">
         <v>0</v>
       </c>
-      <c r="Z64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:28">
+    </row>
+    <row r="65" spans="1:27">
       <c r="A65" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B65" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C65" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D65" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F65" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G65" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J65">
         <v>18</v>
@@ -4479,58 +4285,55 @@
       <c r="K65">
         <v>1.222222</v>
       </c>
-      <c r="M65" t="s">
-        <v>34</v>
-      </c>
-      <c r="N65">
-        <v>0</v>
+      <c r="M65">
+        <v>149</v>
+      </c>
+      <c r="N65" t="s">
+        <v>33</v>
       </c>
       <c r="O65">
         <v>14</v>
       </c>
       <c r="P65" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q65" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q65">
+        <v>22</v>
       </c>
       <c r="R65">
-        <v>22</v>
-      </c>
-      <c r="S65">
         <v>636.363636</v>
       </c>
+      <c r="W65">
+        <v>0</v>
+      </c>
       <c r="X65">
         <v>0</v>
       </c>
       <c r="Y65">
         <v>0</v>
       </c>
-      <c r="Z65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:28">
+    </row>
+    <row r="66" spans="1:27">
       <c r="A66" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B66" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C66" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D66" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E66" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F66" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G66" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J66">
         <v>13</v>
@@ -4538,58 +4341,55 @@
       <c r="K66">
         <v>1</v>
       </c>
-      <c r="M66" t="s">
-        <v>34</v>
-      </c>
-      <c r="N66">
-        <v>0</v>
+      <c r="M66">
+        <v>149</v>
+      </c>
+      <c r="N66" t="s">
+        <v>33</v>
       </c>
       <c r="O66">
         <v>7</v>
       </c>
       <c r="P66" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q66" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q66">
+        <v>13</v>
       </c>
       <c r="R66">
-        <v>13</v>
-      </c>
-      <c r="S66">
         <v>538.461538</v>
       </c>
+      <c r="W66">
+        <v>0</v>
+      </c>
       <c r="X66">
         <v>0</v>
       </c>
       <c r="Y66">
         <v>0</v>
       </c>
-      <c r="Z66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:28">
+    </row>
+    <row r="67" spans="1:27">
       <c r="A67" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B67" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C67" t="s">
+        <v>28</v>
+      </c>
+      <c r="D67" t="s">
         <v>29</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>30</v>
       </c>
-      <c r="E67" t="s">
-        <v>31</v>
-      </c>
       <c r="F67" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G67" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -4597,58 +4397,55 @@
       <c r="K67">
         <v>1</v>
       </c>
-      <c r="M67" t="s">
-        <v>34</v>
-      </c>
-      <c r="N67">
-        <v>0</v>
+      <c r="M67">
+        <v>149</v>
+      </c>
+      <c r="N67" t="s">
+        <v>33</v>
       </c>
       <c r="O67">
         <v>2</v>
       </c>
       <c r="P67" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q67" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q67">
+        <v>1</v>
       </c>
       <c r="R67">
-        <v>1</v>
-      </c>
-      <c r="S67">
         <v>2000</v>
       </c>
+      <c r="W67">
+        <v>0</v>
+      </c>
       <c r="X67">
         <v>0</v>
       </c>
       <c r="Y67">
         <v>0</v>
       </c>
-      <c r="Z67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:28">
+    </row>
+    <row r="68" spans="1:27">
       <c r="A68" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B68" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C68" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68" t="s">
         <v>29</v>
       </c>
-      <c r="D68" t="s">
-        <v>30</v>
-      </c>
       <c r="E68" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F68" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G68" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J68">
         <v>8</v>
@@ -4656,58 +4453,55 @@
       <c r="K68">
         <v>1</v>
       </c>
-      <c r="M68" t="s">
-        <v>34</v>
-      </c>
-      <c r="N68">
-        <v>0</v>
+      <c r="M68">
+        <v>149</v>
+      </c>
+      <c r="N68" t="s">
+        <v>33</v>
       </c>
       <c r="O68">
         <v>4</v>
       </c>
       <c r="P68" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q68" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q68">
+        <v>8</v>
+      </c>
+      <c r="R68">
+        <v>500</v>
+      </c>
+      <c r="W68">
+        <v>0</v>
+      </c>
+      <c r="X68">
+        <v>0</v>
+      </c>
+      <c r="Y68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:27">
+      <c r="A69" t="s">
+        <v>46</v>
+      </c>
+      <c r="B69" t="s">
+        <v>46</v>
+      </c>
+      <c r="C69" t="s">
+        <v>28</v>
+      </c>
+      <c r="D69" t="s">
         <v>35</v>
       </c>
-      <c r="R68">
-        <v>8</v>
-      </c>
-      <c r="S68">
-        <v>500</v>
-      </c>
-      <c r="X68">
-        <v>0</v>
-      </c>
-      <c r="Y68">
-        <v>0</v>
-      </c>
-      <c r="Z68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:28">
-      <c r="A69" t="s">
-        <v>48</v>
-      </c>
-      <c r="B69" t="s">
-        <v>48</v>
-      </c>
-      <c r="C69" t="s">
-        <v>29</v>
-      </c>
-      <c r="D69" t="s">
-        <v>37</v>
-      </c>
       <c r="E69" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F69" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G69" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J69">
         <v>8</v>
@@ -4715,58 +4509,55 @@
       <c r="K69">
         <v>1</v>
       </c>
-      <c r="M69" t="s">
-        <v>34</v>
-      </c>
-      <c r="N69">
-        <v>0</v>
+      <c r="M69">
+        <v>149</v>
+      </c>
+      <c r="N69" t="s">
+        <v>33</v>
       </c>
       <c r="O69">
         <v>11</v>
       </c>
       <c r="P69" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q69" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q69">
+        <v>8</v>
+      </c>
+      <c r="R69">
+        <v>1375</v>
+      </c>
+      <c r="W69">
+        <v>0</v>
+      </c>
+      <c r="X69">
+        <v>0</v>
+      </c>
+      <c r="Y69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:27">
+      <c r="A70" t="s">
+        <v>46</v>
+      </c>
+      <c r="B70" t="s">
+        <v>46</v>
+      </c>
+      <c r="C70" t="s">
+        <v>28</v>
+      </c>
+      <c r="D70" t="s">
         <v>35</v>
       </c>
-      <c r="R69">
-        <v>8</v>
-      </c>
-      <c r="S69">
-        <v>1375</v>
-      </c>
-      <c r="X69">
-        <v>0</v>
-      </c>
-      <c r="Y69">
-        <v>0</v>
-      </c>
-      <c r="Z69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:28">
-      <c r="A70" t="s">
-        <v>48</v>
-      </c>
-      <c r="B70" t="s">
-        <v>48</v>
-      </c>
-      <c r="C70" t="s">
-        <v>29</v>
-      </c>
-      <c r="D70" t="s">
-        <v>37</v>
-      </c>
       <c r="E70" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F70" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G70" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J70">
         <v>11</v>
@@ -4774,58 +4565,55 @@
       <c r="K70">
         <v>1</v>
       </c>
-      <c r="M70" t="s">
-        <v>34</v>
-      </c>
-      <c r="N70">
-        <v>0</v>
+      <c r="M70">
+        <v>149</v>
+      </c>
+      <c r="N70" t="s">
+        <v>33</v>
       </c>
       <c r="O70">
         <v>11</v>
       </c>
       <c r="P70" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q70" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q70">
+        <v>11</v>
       </c>
       <c r="R70">
-        <v>11</v>
-      </c>
-      <c r="S70">
         <v>1000</v>
       </c>
+      <c r="W70">
+        <v>0</v>
+      </c>
       <c r="X70">
         <v>0</v>
       </c>
       <c r="Y70">
         <v>0</v>
       </c>
-      <c r="Z70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:28">
+    </row>
+    <row r="71" spans="1:27">
       <c r="A71" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B71" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C71" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D71" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E71" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F71" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G71" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J71">
         <v>13</v>
@@ -4833,58 +4621,55 @@
       <c r="K71">
         <v>1.230769</v>
       </c>
-      <c r="M71" t="s">
-        <v>34</v>
-      </c>
-      <c r="N71">
-        <v>0</v>
+      <c r="M71">
+        <v>149</v>
+      </c>
+      <c r="N71" t="s">
+        <v>33</v>
       </c>
       <c r="O71">
         <v>13</v>
       </c>
       <c r="P71" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q71">
+        <v>16</v>
       </c>
       <c r="R71">
-        <v>16</v>
-      </c>
-      <c r="S71">
         <v>812.5</v>
       </c>
+      <c r="W71">
+        <v>0</v>
+      </c>
       <c r="X71">
         <v>0</v>
       </c>
       <c r="Y71">
         <v>0</v>
       </c>
-      <c r="Z71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:28">
+    </row>
+    <row r="72" spans="1:27">
       <c r="A72" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B72" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C72" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D72" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E72" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F72" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G72" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J72">
         <v>14</v>
@@ -4892,58 +4677,55 @@
       <c r="K72">
         <v>1</v>
       </c>
-      <c r="M72" t="s">
-        <v>34</v>
-      </c>
-      <c r="N72">
-        <v>0</v>
+      <c r="M72">
+        <v>149</v>
+      </c>
+      <c r="N72" t="s">
+        <v>33</v>
       </c>
       <c r="O72">
         <v>13</v>
       </c>
       <c r="P72" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q72" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q72">
+        <v>14</v>
       </c>
       <c r="R72">
-        <v>14</v>
-      </c>
-      <c r="S72">
         <v>928.571429</v>
       </c>
+      <c r="W72">
+        <v>0</v>
+      </c>
       <c r="X72">
         <v>0</v>
       </c>
       <c r="Y72">
         <v>0</v>
       </c>
-      <c r="Z72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:28">
+    </row>
+    <row r="73" spans="1:27">
       <c r="A73" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B73" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C73" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D73" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E73" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F73" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G73" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J73">
         <v>13</v>
@@ -4951,64 +4733,61 @@
       <c r="K73">
         <v>1.153846</v>
       </c>
-      <c r="M73" t="s">
-        <v>34</v>
-      </c>
-      <c r="N73">
-        <v>0</v>
+      <c r="M73">
+        <v>149</v>
+      </c>
+      <c r="N73" t="s">
+        <v>33</v>
       </c>
       <c r="O73">
         <v>17</v>
       </c>
       <c r="P73" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q73" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q73">
+        <v>15</v>
       </c>
       <c r="R73">
-        <v>15</v>
-      </c>
-      <c r="S73">
         <v>1133.333333</v>
       </c>
+      <c r="W73">
+        <v>0</v>
+      </c>
       <c r="X73">
         <v>0</v>
       </c>
       <c r="Y73">
         <v>0</v>
       </c>
-      <c r="Z73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:28">
+    </row>
+    <row r="74" spans="1:27">
       <c r="A74" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B74" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C74" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D74" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E74" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F74" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G74" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H74">
         <v>1</v>
       </c>
       <c r="I74" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J74">
         <v>18</v>
@@ -5019,67 +4798,64 @@
       <c r="L74">
         <v>16</v>
       </c>
-      <c r="M74" t="s">
-        <v>34</v>
-      </c>
-      <c r="N74">
-        <v>0</v>
+      <c r="M74">
+        <v>149</v>
+      </c>
+      <c r="N74" t="s">
+        <v>33</v>
       </c>
       <c r="O74">
         <v>16</v>
       </c>
       <c r="P74" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q74" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q74">
+        <v>18</v>
       </c>
       <c r="R74">
-        <v>18</v>
+        <v>888.888889</v>
       </c>
       <c r="S74">
-        <v>888.888889</v>
-      </c>
-      <c r="T74">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="U74">
+        <v>16</v>
       </c>
       <c r="V74">
+        <v>5.555556</v>
+      </c>
+      <c r="W74">
+        <v>1</v>
+      </c>
+      <c r="X74">
+        <v>5.555556</v>
+      </c>
+      <c r="Y74">
         <v>16</v>
       </c>
-      <c r="W74">
-        <v>5.555556</v>
-      </c>
-      <c r="X74">
-        <v>1</v>
-      </c>
-      <c r="Y74">
-        <v>5.555556</v>
-      </c>
-      <c r="Z74">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="75" spans="1:28">
+    </row>
+    <row r="75" spans="1:27">
       <c r="A75" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B75" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C75" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D75" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E75" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F75" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G75" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J75">
         <v>15</v>
@@ -5087,58 +4863,55 @@
       <c r="K75">
         <v>1.066667</v>
       </c>
-      <c r="M75" t="s">
-        <v>34</v>
-      </c>
-      <c r="N75">
-        <v>0</v>
+      <c r="M75">
+        <v>149</v>
+      </c>
+      <c r="N75" t="s">
+        <v>33</v>
       </c>
       <c r="O75">
         <v>10</v>
       </c>
       <c r="P75" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q75" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q75">
+        <v>16</v>
       </c>
       <c r="R75">
-        <v>16</v>
-      </c>
-      <c r="S75">
         <v>625</v>
       </c>
+      <c r="W75">
+        <v>0</v>
+      </c>
       <c r="X75">
         <v>0</v>
       </c>
       <c r="Y75">
         <v>0</v>
       </c>
-      <c r="Z75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:28">
+    </row>
+    <row r="76" spans="1:27">
       <c r="A76" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B76" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C76" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D76" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E76" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F76" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G76" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J76">
         <v>17</v>
@@ -5146,58 +4919,55 @@
       <c r="K76">
         <v>1.058824</v>
       </c>
-      <c r="M76" t="s">
-        <v>34</v>
-      </c>
-      <c r="N76">
-        <v>0</v>
+      <c r="M76">
+        <v>149</v>
+      </c>
+      <c r="N76" t="s">
+        <v>33</v>
       </c>
       <c r="O76">
         <v>12</v>
       </c>
       <c r="P76" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q76" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q76">
+        <v>18</v>
       </c>
       <c r="R76">
-        <v>18</v>
-      </c>
-      <c r="S76">
         <v>666.666667</v>
       </c>
+      <c r="W76">
+        <v>0</v>
+      </c>
       <c r="X76">
         <v>0</v>
       </c>
       <c r="Y76">
         <v>0</v>
       </c>
-      <c r="Z76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:28">
+    </row>
+    <row r="77" spans="1:27">
       <c r="A77" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B77" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C77" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D77" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E77" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F77" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G77" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J77">
         <v>10</v>
@@ -5205,58 +4975,55 @@
       <c r="K77">
         <v>1.3</v>
       </c>
-      <c r="M77" t="s">
-        <v>34</v>
-      </c>
-      <c r="N77">
-        <v>0</v>
+      <c r="M77">
+        <v>149</v>
+      </c>
+      <c r="N77" t="s">
+        <v>33</v>
       </c>
       <c r="O77">
         <v>9</v>
       </c>
       <c r="P77" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q77" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q77">
+        <v>13</v>
       </c>
       <c r="R77">
-        <v>13</v>
-      </c>
-      <c r="S77">
         <v>692.307692</v>
       </c>
+      <c r="W77">
+        <v>0</v>
+      </c>
       <c r="X77">
         <v>0</v>
       </c>
       <c r="Y77">
         <v>0</v>
       </c>
-      <c r="Z77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:28">
+    </row>
+    <row r="78" spans="1:27">
       <c r="A78" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B78" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C78" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D78" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E78" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F78" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G78" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J78">
         <v>13</v>
@@ -5264,58 +5031,55 @@
       <c r="K78">
         <v>1.076923</v>
       </c>
-      <c r="M78" t="s">
-        <v>34</v>
-      </c>
-      <c r="N78">
-        <v>0</v>
+      <c r="M78">
+        <v>149</v>
+      </c>
+      <c r="N78" t="s">
+        <v>33</v>
       </c>
       <c r="O78">
         <v>12</v>
       </c>
       <c r="P78" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q78" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q78">
+        <v>14</v>
       </c>
       <c r="R78">
-        <v>14</v>
-      </c>
-      <c r="S78">
         <v>857.142857</v>
       </c>
+      <c r="W78">
+        <v>0</v>
+      </c>
       <c r="X78">
         <v>0</v>
       </c>
       <c r="Y78">
         <v>0</v>
       </c>
-      <c r="Z78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:28">
+    </row>
+    <row r="79" spans="1:27">
       <c r="A79" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B79" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C79" t="s">
+        <v>28</v>
+      </c>
+      <c r="D79" t="s">
         <v>29</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
         <v>30</v>
       </c>
-      <c r="E79" t="s">
-        <v>31</v>
-      </c>
       <c r="F79" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G79" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J79">
         <v>2</v>
@@ -5323,58 +5087,55 @@
       <c r="K79">
         <v>1</v>
       </c>
-      <c r="M79" t="s">
-        <v>34</v>
-      </c>
-      <c r="N79">
-        <v>0</v>
+      <c r="M79">
+        <v>149</v>
+      </c>
+      <c r="N79" t="s">
+        <v>33</v>
       </c>
       <c r="O79">
         <v>4</v>
       </c>
       <c r="P79" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q79" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q79">
+        <v>2</v>
       </c>
       <c r="R79">
-        <v>2</v>
-      </c>
-      <c r="S79">
         <v>2000</v>
       </c>
+      <c r="W79">
+        <v>0</v>
+      </c>
       <c r="X79">
         <v>0</v>
       </c>
       <c r="Y79">
         <v>0</v>
       </c>
-      <c r="Z79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:28">
+    </row>
+    <row r="80" spans="1:27">
       <c r="A80" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B80" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C80" t="s">
+        <v>28</v>
+      </c>
+      <c r="D80" t="s">
         <v>29</v>
       </c>
-      <c r="D80" t="s">
-        <v>30</v>
-      </c>
       <c r="E80" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F80" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G80" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J80">
         <v>6</v>
@@ -5382,58 +5143,55 @@
       <c r="K80">
         <v>1</v>
       </c>
-      <c r="M80" t="s">
-        <v>34</v>
-      </c>
-      <c r="N80">
-        <v>0</v>
+      <c r="M80">
+        <v>149</v>
+      </c>
+      <c r="N80" t="s">
+        <v>33</v>
       </c>
       <c r="O80">
         <v>13</v>
       </c>
       <c r="P80" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q80" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q80">
+        <v>6</v>
+      </c>
+      <c r="R80">
+        <v>2166.666667</v>
+      </c>
+      <c r="W80">
+        <v>0</v>
+      </c>
+      <c r="X80">
+        <v>0</v>
+      </c>
+      <c r="Y80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:27">
+      <c r="A81" t="s">
+        <v>47</v>
+      </c>
+      <c r="B81" t="s">
+        <v>47</v>
+      </c>
+      <c r="C81" t="s">
+        <v>28</v>
+      </c>
+      <c r="D81" t="s">
         <v>35</v>
       </c>
-      <c r="R80">
-        <v>6</v>
-      </c>
-      <c r="S80">
-        <v>2166.666667</v>
-      </c>
-      <c r="X80">
-        <v>0</v>
-      </c>
-      <c r="Y80">
-        <v>0</v>
-      </c>
-      <c r="Z80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:28">
-      <c r="A81" t="s">
-        <v>49</v>
-      </c>
-      <c r="B81" t="s">
-        <v>49</v>
-      </c>
-      <c r="C81" t="s">
-        <v>29</v>
-      </c>
-      <c r="D81" t="s">
-        <v>37</v>
-      </c>
       <c r="E81" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F81" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G81" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J81">
         <v>8</v>
@@ -5441,58 +5199,55 @@
       <c r="K81">
         <v>1</v>
       </c>
-      <c r="M81" t="s">
-        <v>34</v>
-      </c>
-      <c r="N81">
-        <v>0</v>
+      <c r="M81">
+        <v>149</v>
+      </c>
+      <c r="N81" t="s">
+        <v>33</v>
       </c>
       <c r="O81">
         <v>4</v>
       </c>
       <c r="P81" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q81" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q81">
+        <v>8</v>
+      </c>
+      <c r="R81">
+        <v>500</v>
+      </c>
+      <c r="W81">
+        <v>0</v>
+      </c>
+      <c r="X81">
+        <v>0</v>
+      </c>
+      <c r="Y81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:27">
+      <c r="A82" t="s">
+        <v>47</v>
+      </c>
+      <c r="B82" t="s">
+        <v>47</v>
+      </c>
+      <c r="C82" t="s">
+        <v>28</v>
+      </c>
+      <c r="D82" t="s">
         <v>35</v>
       </c>
-      <c r="R81">
-        <v>8</v>
-      </c>
-      <c r="S81">
-        <v>500</v>
-      </c>
-      <c r="X81">
-        <v>0</v>
-      </c>
-      <c r="Y81">
-        <v>0</v>
-      </c>
-      <c r="Z81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:28">
-      <c r="A82" t="s">
-        <v>49</v>
-      </c>
-      <c r="B82" t="s">
-        <v>49</v>
-      </c>
-      <c r="C82" t="s">
-        <v>29</v>
-      </c>
-      <c r="D82" t="s">
-        <v>37</v>
-      </c>
       <c r="E82" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F82" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G82" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J82">
         <v>4</v>
@@ -5500,58 +5255,55 @@
       <c r="K82">
         <v>1</v>
       </c>
-      <c r="M82" t="s">
-        <v>34</v>
-      </c>
-      <c r="N82">
-        <v>0</v>
+      <c r="M82">
+        <v>149</v>
+      </c>
+      <c r="N82" t="s">
+        <v>33</v>
       </c>
       <c r="O82">
         <v>14</v>
       </c>
       <c r="P82" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q82" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q82">
+        <v>4</v>
       </c>
       <c r="R82">
-        <v>4</v>
-      </c>
-      <c r="S82">
         <v>3500</v>
       </c>
+      <c r="W82">
+        <v>0</v>
+      </c>
       <c r="X82">
         <v>0</v>
       </c>
       <c r="Y82">
         <v>0</v>
       </c>
-      <c r="Z82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:28">
+    </row>
+    <row r="83" spans="1:27">
       <c r="A83" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B83" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C83" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D83" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E83" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F83" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G83" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J83">
         <v>13</v>
@@ -5559,64 +5311,61 @@
       <c r="K83">
         <v>1</v>
       </c>
-      <c r="M83" t="s">
-        <v>34</v>
-      </c>
-      <c r="N83">
-        <v>0</v>
+      <c r="M83">
+        <v>149</v>
+      </c>
+      <c r="N83" t="s">
+        <v>33</v>
       </c>
       <c r="O83">
         <v>14</v>
       </c>
       <c r="P83" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q83" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q83">
+        <v>13</v>
       </c>
       <c r="R83">
-        <v>13</v>
-      </c>
-      <c r="S83">
         <v>1076.923077</v>
       </c>
+      <c r="W83">
+        <v>0</v>
+      </c>
       <c r="X83">
         <v>0</v>
       </c>
       <c r="Y83">
         <v>0</v>
       </c>
-      <c r="Z83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:28">
+    </row>
+    <row r="84" spans="1:27">
       <c r="A84" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B84" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C84" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D84" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E84" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F84" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G84" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H84">
         <v>1</v>
       </c>
       <c r="I84" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J84">
         <v>12</v>
@@ -5627,73 +5376,70 @@
       <c r="L84">
         <v>43</v>
       </c>
-      <c r="M84" t="s">
-        <v>34</v>
-      </c>
-      <c r="N84">
-        <v>0</v>
+      <c r="M84">
+        <v>149</v>
+      </c>
+      <c r="N84" t="s">
+        <v>33</v>
       </c>
       <c r="O84">
         <v>43</v>
       </c>
       <c r="P84" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q84" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q84">
+        <v>12</v>
       </c>
       <c r="R84">
-        <v>12</v>
+        <v>3583.333333</v>
       </c>
       <c r="S84">
-        <v>3583.333333</v>
-      </c>
-      <c r="T84">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="U84">
+        <v>43</v>
       </c>
       <c r="V84">
+        <v>8.333333</v>
+      </c>
+      <c r="W84">
+        <v>1</v>
+      </c>
+      <c r="X84">
+        <v>8.333333</v>
+      </c>
+      <c r="Y84">
         <v>43</v>
       </c>
-      <c r="W84">
-        <v>8.333333</v>
-      </c>
-      <c r="X84">
-        <v>1</v>
-      </c>
-      <c r="Y84">
-        <v>8.333333</v>
-      </c>
-      <c r="Z84">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="85" spans="1:28">
+    </row>
+    <row r="85" spans="1:27">
       <c r="A85" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B85" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C85" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D85" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E85" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F85" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G85" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H85">
         <v>1</v>
       </c>
       <c r="I85" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J85">
         <v>3</v>
@@ -5704,67 +5450,64 @@
       <c r="L85">
         <v>3</v>
       </c>
-      <c r="M85" t="s">
-        <v>34</v>
-      </c>
-      <c r="N85">
-        <v>0</v>
+      <c r="M85">
+        <v>149</v>
+      </c>
+      <c r="N85" t="s">
+        <v>33</v>
       </c>
       <c r="O85">
         <v>3</v>
       </c>
       <c r="P85" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q85" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q85">
+        <v>3</v>
       </c>
       <c r="R85">
+        <v>1000</v>
+      </c>
+      <c r="S85">
+        <v>1</v>
+      </c>
+      <c r="U85">
         <v>3</v>
       </c>
-      <c r="S85">
-        <v>1000</v>
-      </c>
-      <c r="T85">
-        <v>1</v>
-      </c>
       <c r="V85">
+        <v>33.333333</v>
+      </c>
+      <c r="W85">
+        <v>1</v>
+      </c>
+      <c r="X85">
+        <v>33.333333</v>
+      </c>
+      <c r="Y85">
         <v>3</v>
       </c>
-      <c r="W85">
-        <v>33.333333</v>
-      </c>
-      <c r="X85">
-        <v>1</v>
-      </c>
-      <c r="Y85">
-        <v>33.333333</v>
-      </c>
-      <c r="Z85">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="86" spans="1:28">
+    </row>
+    <row r="86" spans="1:27">
       <c r="A86" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B86" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C86" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D86" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E86" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F86" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G86" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J86">
         <v>8</v>
@@ -5772,58 +5515,55 @@
       <c r="K86">
         <v>1.25</v>
       </c>
-      <c r="M86" t="s">
-        <v>34</v>
-      </c>
-      <c r="N86">
-        <v>0</v>
+      <c r="M86">
+        <v>149</v>
+      </c>
+      <c r="N86" t="s">
+        <v>33</v>
       </c>
       <c r="O86">
         <v>11</v>
       </c>
       <c r="P86" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q86" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q86">
+        <v>10</v>
       </c>
       <c r="R86">
-        <v>10</v>
-      </c>
-      <c r="S86">
         <v>1100</v>
       </c>
+      <c r="W86">
+        <v>0</v>
+      </c>
       <c r="X86">
         <v>0</v>
       </c>
       <c r="Y86">
         <v>0</v>
       </c>
-      <c r="Z86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:28">
+    </row>
+    <row r="87" spans="1:27">
       <c r="A87" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B87" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C87" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D87" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E87" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F87" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G87" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J87">
         <v>10</v>
@@ -5831,58 +5571,55 @@
       <c r="K87">
         <v>1.4</v>
       </c>
-      <c r="M87" t="s">
-        <v>34</v>
-      </c>
-      <c r="N87">
-        <v>0</v>
+      <c r="M87">
+        <v>149</v>
+      </c>
+      <c r="N87" t="s">
+        <v>33</v>
       </c>
       <c r="O87">
         <v>10</v>
       </c>
       <c r="P87" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q87" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q87">
+        <v>14</v>
       </c>
       <c r="R87">
-        <v>14</v>
-      </c>
-      <c r="S87">
         <v>714.285714</v>
       </c>
+      <c r="W87">
+        <v>0</v>
+      </c>
       <c r="X87">
         <v>0</v>
       </c>
       <c r="Y87">
         <v>0</v>
       </c>
-      <c r="Z87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:28">
+    </row>
+    <row r="88" spans="1:27">
       <c r="A88" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B88" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C88" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D88" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E88" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F88" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G88" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J88">
         <v>9</v>
@@ -5890,58 +5627,55 @@
       <c r="K88">
         <v>1.111111</v>
       </c>
-      <c r="M88" t="s">
-        <v>34</v>
-      </c>
-      <c r="N88">
-        <v>0</v>
+      <c r="M88">
+        <v>149</v>
+      </c>
+      <c r="N88" t="s">
+        <v>33</v>
       </c>
       <c r="O88">
         <v>9</v>
       </c>
       <c r="P88" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q88" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q88">
+        <v>10</v>
       </c>
       <c r="R88">
-        <v>10</v>
-      </c>
-      <c r="S88">
         <v>900</v>
       </c>
+      <c r="W88">
+        <v>0</v>
+      </c>
       <c r="X88">
         <v>0</v>
       </c>
       <c r="Y88">
         <v>0</v>
       </c>
-      <c r="Z88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:28">
+    </row>
+    <row r="89" spans="1:27">
       <c r="A89" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B89" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C89" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D89" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E89" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F89" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G89" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J89">
         <v>11</v>
@@ -5949,58 +5683,55 @@
       <c r="K89">
         <v>1</v>
       </c>
-      <c r="M89" t="s">
-        <v>34</v>
-      </c>
-      <c r="N89">
-        <v>0</v>
+      <c r="M89">
+        <v>149</v>
+      </c>
+      <c r="N89" t="s">
+        <v>33</v>
       </c>
       <c r="O89">
         <v>6</v>
       </c>
       <c r="P89" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q89" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q89">
+        <v>11</v>
       </c>
       <c r="R89">
-        <v>11</v>
-      </c>
-      <c r="S89">
         <v>545.454545</v>
       </c>
+      <c r="W89">
+        <v>0</v>
+      </c>
       <c r="X89">
         <v>0</v>
       </c>
       <c r="Y89">
         <v>0</v>
       </c>
-      <c r="Z89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:28">
+    </row>
+    <row r="90" spans="1:27">
       <c r="A90" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C90" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D90" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E90" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F90" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G90" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J90">
         <v>8</v>
@@ -6008,58 +5739,55 @@
       <c r="K90">
         <v>1</v>
       </c>
-      <c r="M90" t="s">
-        <v>34</v>
-      </c>
-      <c r="N90">
-        <v>0</v>
+      <c r="M90">
+        <v>149</v>
+      </c>
+      <c r="N90" t="s">
+        <v>33</v>
       </c>
       <c r="O90">
         <v>4</v>
       </c>
       <c r="P90" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q90" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q90">
+        <v>8</v>
       </c>
       <c r="R90">
-        <v>8</v>
-      </c>
-      <c r="S90">
         <v>500</v>
       </c>
+      <c r="W90">
+        <v>0</v>
+      </c>
       <c r="X90">
         <v>0</v>
       </c>
       <c r="Y90">
         <v>0</v>
       </c>
-      <c r="Z90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:28">
+    </row>
+    <row r="91" spans="1:27">
       <c r="A91" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B91" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C91" t="s">
+        <v>28</v>
+      </c>
+      <c r="D91" t="s">
         <v>29</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
         <v>30</v>
       </c>
-      <c r="E91" t="s">
-        <v>31</v>
-      </c>
       <c r="F91" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G91" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J91">
         <v>1</v>
@@ -6067,58 +5795,55 @@
       <c r="K91">
         <v>1</v>
       </c>
-      <c r="M91" t="s">
+      <c r="M91">
+        <v>149</v>
+      </c>
+      <c r="N91" t="s">
+        <v>33</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q91">
+        <v>1</v>
+      </c>
+      <c r="R91">
+        <v>0</v>
+      </c>
+      <c r="W91">
+        <v>0</v>
+      </c>
+      <c r="X91">
+        <v>0</v>
+      </c>
+      <c r="Y91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:27">
+      <c r="A92" t="s">
+        <v>48</v>
+      </c>
+      <c r="B92" t="s">
+        <v>48</v>
+      </c>
+      <c r="C92" t="s">
+        <v>28</v>
+      </c>
+      <c r="D92" t="s">
+        <v>29</v>
+      </c>
+      <c r="E92" t="s">
         <v>34</v>
       </c>
-      <c r="N91">
-        <v>0</v>
-      </c>
-      <c r="O91">
-        <v>0</v>
-      </c>
-      <c r="P91" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q91" t="s">
-        <v>35</v>
-      </c>
-      <c r="R91">
-        <v>1</v>
-      </c>
-      <c r="S91">
-        <v>0</v>
-      </c>
-      <c r="X91">
-        <v>0</v>
-      </c>
-      <c r="Y91">
-        <v>0</v>
-      </c>
-      <c r="Z91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:28">
-      <c r="A92" t="s">
-        <v>35</v>
-      </c>
-      <c r="B92" t="s">
-        <v>35</v>
-      </c>
-      <c r="C92" t="s">
-        <v>29</v>
-      </c>
-      <c r="D92" t="s">
-        <v>30</v>
-      </c>
-      <c r="E92" t="s">
-        <v>36</v>
-      </c>
       <c r="F92" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G92" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J92">
         <v>4</v>
@@ -6126,58 +5851,55 @@
       <c r="K92">
         <v>1</v>
       </c>
-      <c r="M92" t="s">
-        <v>34</v>
-      </c>
-      <c r="N92">
-        <v>0</v>
+      <c r="M92">
+        <v>149</v>
+      </c>
+      <c r="N92" t="s">
+        <v>33</v>
       </c>
       <c r="O92">
         <v>15</v>
       </c>
       <c r="P92" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q92" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q92">
+        <v>4</v>
+      </c>
+      <c r="R92">
+        <v>3750</v>
+      </c>
+      <c r="W92">
+        <v>0</v>
+      </c>
+      <c r="X92">
+        <v>0</v>
+      </c>
+      <c r="Y92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:27">
+      <c r="A93" t="s">
+        <v>48</v>
+      </c>
+      <c r="B93" t="s">
+        <v>48</v>
+      </c>
+      <c r="C93" t="s">
+        <v>28</v>
+      </c>
+      <c r="D93" t="s">
         <v>35</v>
       </c>
-      <c r="R92">
-        <v>4</v>
-      </c>
-      <c r="S92">
-        <v>3750</v>
-      </c>
-      <c r="X92">
-        <v>0</v>
-      </c>
-      <c r="Y92">
-        <v>0</v>
-      </c>
-      <c r="Z92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:28">
-      <c r="A93" t="s">
-        <v>35</v>
-      </c>
-      <c r="B93" t="s">
-        <v>35</v>
-      </c>
-      <c r="C93" t="s">
-        <v>29</v>
-      </c>
-      <c r="D93" t="s">
-        <v>37</v>
-      </c>
       <c r="E93" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F93" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G93" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J93">
         <v>4</v>
@@ -6185,58 +5907,55 @@
       <c r="K93">
         <v>1.25</v>
       </c>
-      <c r="M93" t="s">
-        <v>34</v>
-      </c>
-      <c r="N93">
-        <v>0</v>
+      <c r="M93">
+        <v>149</v>
+      </c>
+      <c r="N93" t="s">
+        <v>33</v>
       </c>
       <c r="O93">
         <v>3</v>
       </c>
       <c r="P93" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q93" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q93">
+        <v>5</v>
+      </c>
+      <c r="R93">
+        <v>600</v>
+      </c>
+      <c r="W93">
+        <v>0</v>
+      </c>
+      <c r="X93">
+        <v>0</v>
+      </c>
+      <c r="Y93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:27">
+      <c r="A94" t="s">
+        <v>48</v>
+      </c>
+      <c r="B94" t="s">
+        <v>48</v>
+      </c>
+      <c r="C94" t="s">
+        <v>28</v>
+      </c>
+      <c r="D94" t="s">
         <v>35</v>
       </c>
-      <c r="R93">
-        <v>5</v>
-      </c>
-      <c r="S93">
-        <v>600</v>
-      </c>
-      <c r="X93">
-        <v>0</v>
-      </c>
-      <c r="Y93">
-        <v>0</v>
-      </c>
-      <c r="Z93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:28">
-      <c r="A94" t="s">
-        <v>35</v>
-      </c>
-      <c r="B94" t="s">
-        <v>35</v>
-      </c>
-      <c r="C94" t="s">
-        <v>29</v>
-      </c>
-      <c r="D94" t="s">
-        <v>37</v>
-      </c>
       <c r="E94" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F94" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G94" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J94">
         <v>4</v>
@@ -6244,58 +5963,55 @@
       <c r="K94">
         <v>1</v>
       </c>
-      <c r="M94" t="s">
-        <v>34</v>
-      </c>
-      <c r="N94">
-        <v>0</v>
+      <c r="M94">
+        <v>149</v>
+      </c>
+      <c r="N94" t="s">
+        <v>33</v>
       </c>
       <c r="O94">
         <v>10</v>
       </c>
       <c r="P94" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q94" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q94">
+        <v>4</v>
       </c>
       <c r="R94">
-        <v>4</v>
-      </c>
-      <c r="S94">
         <v>2500</v>
       </c>
+      <c r="W94">
+        <v>0</v>
+      </c>
       <c r="X94">
         <v>0</v>
       </c>
       <c r="Y94">
         <v>0</v>
       </c>
-      <c r="Z94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:28">
+    </row>
+    <row r="95" spans="1:27">
       <c r="A95" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C95" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D95" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E95" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F95" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G95" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J95">
         <v>8</v>
@@ -6303,64 +6019,61 @@
       <c r="K95">
         <v>1</v>
       </c>
-      <c r="M95" t="s">
-        <v>34</v>
-      </c>
-      <c r="N95">
-        <v>0</v>
+      <c r="M95">
+        <v>149</v>
+      </c>
+      <c r="N95" t="s">
+        <v>33</v>
       </c>
       <c r="O95">
         <v>10</v>
       </c>
       <c r="P95" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q95" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q95">
+        <v>8</v>
       </c>
       <c r="R95">
-        <v>8</v>
-      </c>
-      <c r="S95">
         <v>1250</v>
       </c>
+      <c r="W95">
+        <v>0</v>
+      </c>
       <c r="X95">
         <v>0</v>
       </c>
       <c r="Y95">
         <v>0</v>
       </c>
-      <c r="Z95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:28">
+    </row>
+    <row r="96" spans="1:27">
       <c r="A96" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C96" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D96" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E96" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F96" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G96" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H96">
         <v>1</v>
       </c>
       <c r="I96" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J96">
         <v>8</v>
@@ -6371,67 +6084,64 @@
       <c r="L96">
         <v>7</v>
       </c>
-      <c r="M96" t="s">
-        <v>34</v>
-      </c>
-      <c r="N96">
-        <v>0</v>
+      <c r="M96">
+        <v>149</v>
+      </c>
+      <c r="N96" t="s">
+        <v>33</v>
       </c>
       <c r="O96">
         <v>7</v>
       </c>
       <c r="P96" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q96" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q96">
+        <v>8</v>
       </c>
       <c r="R96">
-        <v>8</v>
+        <v>875</v>
       </c>
       <c r="S96">
-        <v>875</v>
-      </c>
-      <c r="T96">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="U96">
+        <v>7</v>
       </c>
       <c r="V96">
+        <v>12.5</v>
+      </c>
+      <c r="W96">
+        <v>1</v>
+      </c>
+      <c r="X96">
+        <v>12.5</v>
+      </c>
+      <c r="Y96">
         <v>7</v>
       </c>
-      <c r="W96">
-        <v>12.5</v>
-      </c>
-      <c r="X96">
-        <v>1</v>
-      </c>
-      <c r="Y96">
-        <v>12.5</v>
-      </c>
-      <c r="Z96">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="97" spans="1:28">
+    </row>
+    <row r="97" spans="1:27">
       <c r="A97" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B97" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C97" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D97" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E97" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F97" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G97" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J97">
         <v>4</v>
@@ -6439,58 +6149,55 @@
       <c r="K97">
         <v>1</v>
       </c>
-      <c r="M97" t="s">
-        <v>34</v>
-      </c>
-      <c r="N97">
-        <v>0</v>
+      <c r="M97">
+        <v>149</v>
+      </c>
+      <c r="N97" t="s">
+        <v>33</v>
       </c>
       <c r="O97">
         <v>2</v>
       </c>
       <c r="P97" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q97" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q97">
+        <v>4</v>
       </c>
       <c r="R97">
-        <v>4</v>
-      </c>
-      <c r="S97">
         <v>500</v>
       </c>
+      <c r="W97">
+        <v>0</v>
+      </c>
       <c r="X97">
         <v>0</v>
       </c>
       <c r="Y97">
         <v>0</v>
       </c>
-      <c r="Z97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:28">
+    </row>
+    <row r="98" spans="1:27">
       <c r="A98" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B98" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C98" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D98" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E98" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F98" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G98" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J98">
         <v>12</v>
@@ -6498,58 +6205,55 @@
       <c r="K98">
         <v>1.083333</v>
       </c>
-      <c r="M98" t="s">
-        <v>34</v>
-      </c>
-      <c r="N98">
-        <v>0</v>
+      <c r="M98">
+        <v>149</v>
+      </c>
+      <c r="N98" t="s">
+        <v>33</v>
       </c>
       <c r="O98">
         <v>9</v>
       </c>
       <c r="P98" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q98" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q98">
+        <v>13</v>
       </c>
       <c r="R98">
-        <v>13</v>
-      </c>
-      <c r="S98">
         <v>692.307692</v>
       </c>
+      <c r="W98">
+        <v>0</v>
+      </c>
       <c r="X98">
         <v>0</v>
       </c>
       <c r="Y98">
         <v>0</v>
       </c>
-      <c r="Z98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:28">
+    </row>
+    <row r="99" spans="1:27">
       <c r="A99" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B99" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C99" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D99" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E99" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F99" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G99" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J99">
         <v>6</v>
@@ -6557,58 +6261,55 @@
       <c r="K99">
         <v>1</v>
       </c>
-      <c r="M99" t="s">
-        <v>34</v>
-      </c>
-      <c r="N99">
-        <v>0</v>
+      <c r="M99">
+        <v>149</v>
+      </c>
+      <c r="N99" t="s">
+        <v>33</v>
       </c>
       <c r="O99">
         <v>4</v>
       </c>
       <c r="P99" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q99" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q99">
+        <v>6</v>
       </c>
       <c r="R99">
-        <v>6</v>
-      </c>
-      <c r="S99">
         <v>666.666667</v>
       </c>
+      <c r="W99">
+        <v>0</v>
+      </c>
       <c r="X99">
         <v>0</v>
       </c>
       <c r="Y99">
         <v>0</v>
       </c>
-      <c r="Z99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:28">
+    </row>
+    <row r="100" spans="1:27">
       <c r="A100" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B100" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C100" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D100" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E100" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F100" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G100" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J100">
         <v>12</v>
@@ -6616,58 +6317,55 @@
       <c r="K100">
         <v>1.083333</v>
       </c>
-      <c r="M100" t="s">
-        <v>34</v>
-      </c>
-      <c r="N100">
-        <v>0</v>
+      <c r="M100">
+        <v>149</v>
+      </c>
+      <c r="N100" t="s">
+        <v>33</v>
       </c>
       <c r="O100">
         <v>6</v>
       </c>
       <c r="P100" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q100" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q100">
+        <v>13</v>
       </c>
       <c r="R100">
-        <v>13</v>
-      </c>
-      <c r="S100">
         <v>461.538462</v>
       </c>
+      <c r="W100">
+        <v>0</v>
+      </c>
       <c r="X100">
         <v>0</v>
       </c>
       <c r="Y100">
         <v>0</v>
       </c>
-      <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:28">
+    </row>
+    <row r="101" spans="1:27">
       <c r="A101" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B101" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C101" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D101" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E101" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F101" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G101" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J101">
         <v>8</v>
@@ -6675,58 +6373,55 @@
       <c r="K101">
         <v>1</v>
       </c>
-      <c r="M101" t="s">
-        <v>34</v>
-      </c>
-      <c r="N101">
-        <v>0</v>
+      <c r="M101">
+        <v>149</v>
+      </c>
+      <c r="N101" t="s">
+        <v>33</v>
       </c>
       <c r="O101">
         <v>10</v>
       </c>
       <c r="P101" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q101" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q101">
+        <v>8</v>
       </c>
       <c r="R101">
-        <v>8</v>
-      </c>
-      <c r="S101">
         <v>1250</v>
       </c>
+      <c r="W101">
+        <v>0</v>
+      </c>
       <c r="X101">
         <v>0</v>
       </c>
       <c r="Y101">
         <v>0</v>
       </c>
-      <c r="Z101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:28">
+    </row>
+    <row r="102" spans="1:27">
       <c r="A102" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B102" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C102" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D102" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E102" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F102" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G102" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J102">
         <v>5</v>
@@ -6734,34 +6429,31 @@
       <c r="K102">
         <v>1</v>
       </c>
-      <c r="M102" t="s">
-        <v>34</v>
-      </c>
-      <c r="N102">
-        <v>0</v>
+      <c r="M102">
+        <v>149</v>
+      </c>
+      <c r="N102" t="s">
+        <v>33</v>
       </c>
       <c r="O102">
         <v>3</v>
       </c>
       <c r="P102" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q102" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="Q102">
+        <v>5</v>
       </c>
       <c r="R102">
-        <v>5</v>
-      </c>
-      <c r="S102">
         <v>600</v>
       </c>
+      <c r="W102">
+        <v>0</v>
+      </c>
       <c r="X102">
         <v>0</v>
       </c>
       <c r="Y102">
-        <v>0</v>
-      </c>
-      <c r="Z102">
         <v>0</v>
       </c>
     </row>
